--- a/resultados_torneo.xlsx
+++ b/resultados_torneo.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Downloads\preubas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43B62724-B271-4AFF-8CBE-9420C20F167E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C44C48B0-3524-4DA7-B946-513DB65FB594}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,12 +16,23 @@
     <sheet name="Resultados" sheetId="1" r:id="rId1"/>
     <sheet name="Pokémon Usage" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="623" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="623" uniqueCount="184">
   <si>
     <t>Semana/Fecha</t>
   </si>
@@ -570,6 +581,9 @@
   </si>
   <si>
     <t>Week</t>
+  </si>
+  <si>
+    <t>Charizard_Mega_Y</t>
   </si>
 </sst>
 </file>
@@ -1080,7 +1094,7 @@
         <v>2</v>
       </c>
       <c r="I2" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>20</v>
@@ -1127,7 +1141,7 @@
         <v>0</v>
       </c>
       <c r="I3" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>27</v>
@@ -1174,7 +1188,7 @@
         <v>2</v>
       </c>
       <c r="I4" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J4" s="5" t="s">
         <v>36</v>
@@ -1221,7 +1235,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J5" s="5" t="s">
         <v>41</v>
@@ -1268,7 +1282,7 @@
         <v>2</v>
       </c>
       <c r="I6" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
@@ -1303,7 +1317,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
@@ -1338,7 +1352,7 @@
         <v>2</v>
       </c>
       <c r="I8" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J8" s="5" t="s">
         <v>53</v>
@@ -1385,7 +1399,7 @@
         <v>0</v>
       </c>
       <c r="I9" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J9" s="5" t="s">
         <v>58</v>
@@ -1432,7 +1446,7 @@
         <v>2</v>
       </c>
       <c r="I10" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>55</v>
@@ -1479,7 +1493,7 @@
         <v>0</v>
       </c>
       <c r="I11" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>66</v>
@@ -1526,7 +1540,7 @@
         <v>2</v>
       </c>
       <c r="I12" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J12" s="5" t="s">
         <v>28</v>
@@ -2022,7 +2036,7 @@
         <v>2</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>91</v>
+        <v>183</v>
       </c>
       <c r="K23" s="2" t="s">
         <v>114</v>
@@ -2374,7 +2388,7 @@
         <v>2</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>91</v>
+        <v>183</v>
       </c>
       <c r="K31" s="2" t="s">
         <v>24</v>
@@ -2467,8 +2481,8 @@
       <c r="I33" s="3">
         <v>2</v>
       </c>
-      <c r="J33" s="5" t="s">
-        <v>91</v>
+      <c r="J33" s="2" t="s">
+        <v>183</v>
       </c>
       <c r="K33" s="5" t="s">
         <v>138</v>
@@ -2987,8 +3001,8 @@
       <c r="J44" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="K44" s="5" t="s">
-        <v>91</v>
+      <c r="K44" s="2" t="s">
+        <v>183</v>
       </c>
       <c r="L44" s="5" t="s">
         <v>25</v>
@@ -3031,8 +3045,8 @@
       <c r="I45" s="3">
         <v>2</v>
       </c>
-      <c r="J45" s="5" t="s">
-        <v>91</v>
+      <c r="J45" s="2" t="s">
+        <v>183</v>
       </c>
       <c r="K45" s="5" t="s">
         <v>20</v>

--- a/resultados_torneo.xlsx
+++ b/resultados_torneo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Downloads\preubas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C44C48B0-3524-4DA7-B946-513DB65FB594}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66CD74EC-B8C4-4D7C-AFFD-2E3A0FFE6C54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/resultados_torneo.xlsx
+++ b/resultados_torneo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Downloads\preubas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66CD74EC-B8C4-4D7C-AFFD-2E3A0FFE6C54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C538805E-6B0C-40C9-8C37-12F63D0F3A3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="623" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="623" uniqueCount="197">
   <si>
     <t>Semana/Fecha</t>
   </si>
@@ -584,6 +584,45 @@
   </si>
   <si>
     <t>Charizard_Mega_Y</t>
+  </si>
+  <si>
+    <t>basculegion_male</t>
+  </si>
+  <si>
+    <t>ninetales_alola</t>
+  </si>
+  <si>
+    <t>gengar mega</t>
+  </si>
+  <si>
+    <t>Garchomp mega</t>
+  </si>
+  <si>
+    <t>Tyranitar Mega</t>
+  </si>
+  <si>
+    <t>Gardevoir mega</t>
+  </si>
+  <si>
+    <t>Scovillan mega</t>
+  </si>
+  <si>
+    <t>rotom_wash</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Aerodactyl Mega</t>
+  </si>
+  <si>
+    <t>Gardevoir Mega</t>
+  </si>
+  <si>
+    <t>Venusaur Mega</t>
+  </si>
+  <si>
+    <t>mimikyu-disguised</t>
+  </si>
+  <si>
+    <t>Scovillain mega</t>
   </si>
 </sst>
 </file>
@@ -1237,11 +1276,11 @@
       <c r="I5" s="3">
         <v>2</v>
       </c>
-      <c r="J5" s="5" t="s">
-        <v>41</v>
+      <c r="J5" s="2" t="s">
+        <v>183</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>42</v>
+        <v>138</v>
       </c>
       <c r="L5" s="5" t="s">
         <v>20</v>
@@ -1646,13 +1685,13 @@
         <v>24</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>25</v>
+        <v>184</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="O14" s="2" t="s">
-        <v>83</v>
+        <v>22</v>
+      </c>
+      <c r="O14" s="5" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
@@ -1684,7 +1723,7 @@
         <v>2</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>85</v>
+        <v>193</v>
       </c>
       <c r="K15" s="2" t="s">
         <v>24</v>
@@ -1696,7 +1735,7 @@
         <v>68</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>25</v>
+        <v>184</v>
       </c>
       <c r="O15" s="2" t="s">
         <v>22</v>
@@ -1734,16 +1773,16 @@
         <v>90</v>
       </c>
       <c r="K16" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="L16" s="5" t="s">
-        <v>91</v>
+        <v>194</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>183</v>
       </c>
       <c r="M16" s="5" t="s">
         <v>31</v>
       </c>
       <c r="N16" s="5" t="s">
-        <v>92</v>
+        <v>184</v>
       </c>
       <c r="O16" s="5" t="s">
         <v>22</v>
@@ -1778,16 +1817,16 @@
         <v>2</v>
       </c>
       <c r="J17" s="5" t="s">
-        <v>94</v>
+        <v>192</v>
       </c>
       <c r="K17" s="5" t="s">
-        <v>95</v>
+        <v>196</v>
       </c>
       <c r="L17" s="5" t="s">
         <v>24</v>
       </c>
       <c r="M17" s="5" t="s">
-        <v>92</v>
+        <v>143</v>
       </c>
       <c r="N17" s="5" t="s">
         <v>22</v>
@@ -1895,7 +1934,7 @@
         <v>2</v>
       </c>
       <c r="J20" s="5" t="s">
-        <v>83</v>
+        <v>138</v>
       </c>
       <c r="K20" s="5" t="s">
         <v>20</v>
@@ -1910,7 +1949,7 @@
         <v>31</v>
       </c>
       <c r="O20" s="5" t="s">
-        <v>25</v>
+        <v>143</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
@@ -1945,13 +1984,13 @@
         <v>105</v>
       </c>
       <c r="K21" s="5" t="s">
-        <v>106</v>
+        <v>191</v>
       </c>
       <c r="L21" s="5" t="s">
         <v>107</v>
       </c>
       <c r="M21" s="5" t="s">
-        <v>108</v>
+        <v>185</v>
       </c>
       <c r="N21" s="5" t="s">
         <v>31</v>
@@ -2095,7 +2134,7 @@
         <v>31</v>
       </c>
       <c r="N24" s="5" t="s">
-        <v>25</v>
+        <v>143</v>
       </c>
       <c r="O24" s="5" t="s">
         <v>90</v>
@@ -2185,8 +2224,8 @@
       <c r="L26" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="M26" s="2" t="s">
-        <v>25</v>
+      <c r="M26" s="5" t="s">
+        <v>143</v>
       </c>
       <c r="N26" s="2" t="s">
         <v>22</v>
@@ -2224,7 +2263,7 @@
         <v>2</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>127</v>
+        <v>185</v>
       </c>
       <c r="K27" s="2" t="s">
         <v>24</v>
@@ -2353,7 +2392,7 @@
         <v>22</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>92</v>
+        <v>184</v>
       </c>
       <c r="O30" s="2" t="s">
         <v>112</v>
@@ -2393,8 +2432,8 @@
       <c r="K31" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="L31" s="2" t="s">
-        <v>92</v>
+      <c r="L31" s="5" t="s">
+        <v>143</v>
       </c>
       <c r="M31" s="2" t="s">
         <v>68</v>
@@ -2450,7 +2489,7 @@
         <v>73</v>
       </c>
       <c r="O32" s="5" t="s">
-        <v>141</v>
+        <v>195</v>
       </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
@@ -2537,8 +2576,8 @@
       <c r="L34" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="M34" s="2" t="s">
-        <v>25</v>
+      <c r="M34" s="5" t="s">
+        <v>143</v>
       </c>
       <c r="N34" s="2" t="s">
         <v>24</v>
@@ -2587,8 +2626,8 @@
       <c r="M35" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="N35" s="2" t="s">
-        <v>25</v>
+      <c r="N35" s="5" t="s">
+        <v>143</v>
       </c>
       <c r="O35" s="2" t="s">
         <v>31</v>
@@ -2632,7 +2671,7 @@
         <v>24</v>
       </c>
       <c r="M36" s="5" t="s">
-        <v>23</v>
+        <v>196</v>
       </c>
       <c r="N36" s="5" t="s">
         <v>32</v>
@@ -2817,7 +2856,7 @@
         <v>94</v>
       </c>
       <c r="L40" s="5" t="s">
-        <v>95</v>
+        <v>190</v>
       </c>
       <c r="M40" s="5" t="s">
         <v>24</v>
@@ -2858,13 +2897,13 @@
         <v>2</v>
       </c>
       <c r="J41" s="5" t="s">
-        <v>166</v>
+        <v>188</v>
       </c>
       <c r="K41" s="5" t="s">
-        <v>167</v>
+        <v>138</v>
       </c>
       <c r="L41" s="5" t="s">
-        <v>106</v>
+        <v>191</v>
       </c>
       <c r="M41" s="5" t="s">
         <v>153</v>
@@ -2908,7 +2947,7 @@
         <v>169</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>85</v>
+        <v>189</v>
       </c>
       <c r="L42" s="2" t="s">
         <v>68</v>
@@ -2917,7 +2956,7 @@
         <v>37</v>
       </c>
       <c r="N42" s="2" t="s">
-        <v>170</v>
+        <v>187</v>
       </c>
       <c r="O42" s="2" t="s">
         <v>38</v>
@@ -2964,7 +3003,7 @@
         <v>73</v>
       </c>
       <c r="N43" s="2" t="s">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="O43" s="2" t="s">
         <v>68</v>
@@ -3005,7 +3044,7 @@
         <v>183</v>
       </c>
       <c r="L44" s="5" t="s">
-        <v>25</v>
+        <v>143</v>
       </c>
       <c r="M44" s="5" t="s">
         <v>31</v>
@@ -3061,7 +3100,7 @@
         <v>39</v>
       </c>
       <c r="O45" s="5" t="s">
-        <v>25</v>
+        <v>143</v>
       </c>
     </row>
   </sheetData>

--- a/resultados_torneo.xlsx
+++ b/resultados_torneo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Downloads\preubas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C538805E-6B0C-40C9-8C37-12F63D0F3A3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12B5ECB0-66CF-4AC6-8BAB-07EE2CA64939}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="623" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="623" uniqueCount="201">
   <si>
     <t>Semana/Fecha</t>
   </si>
@@ -623,6 +623,18 @@
   </si>
   <si>
     <t>Scovillain mega</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Venusaur Mega </t>
+  </si>
+  <si>
+    <t>palafin_hero</t>
+  </si>
+  <si>
+    <t>Froslass Mega</t>
+  </si>
+  <si>
+    <t>maushold_family_of_four</t>
   </si>
 </sst>
 </file>
@@ -1056,7 +1068,8 @@
     <col min="4" max="5" width="16" customWidth="1"/>
     <col min="6" max="6" width="25" customWidth="1"/>
     <col min="7" max="7" width="16" customWidth="1"/>
-    <col min="8" max="9" width="10" customWidth="1"/>
+    <col min="8" max="8" width="10" customWidth="1"/>
+    <col min="9" max="9" width="6.140625" bestFit="1" customWidth="1"/>
     <col min="10" max="15" width="18" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1191,8 +1204,8 @@
       <c r="L3" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="M3" s="2" t="s">
-        <v>30</v>
+      <c r="M3" s="5" t="s">
+        <v>191</v>
       </c>
       <c r="N3" s="2" t="s">
         <v>31</v>
@@ -1394,7 +1407,7 @@
         <v>2</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>53</v>
+        <v>197</v>
       </c>
       <c r="K8" s="5" t="s">
         <v>54</v>
@@ -1597,7 +1610,7 @@
         <v>22</v>
       </c>
       <c r="O12" s="5" t="s">
-        <v>73</v>
+        <v>200</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
@@ -2028,7 +2041,7 @@
         <v>2</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>112</v>
+        <v>36</v>
       </c>
       <c r="K22" s="2" t="s">
         <v>38</v>
@@ -2078,7 +2091,7 @@
         <v>183</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>114</v>
+        <v>199</v>
       </c>
       <c r="L23" s="2" t="s">
         <v>20</v>
@@ -2395,7 +2408,7 @@
         <v>184</v>
       </c>
       <c r="O30" s="2" t="s">
-        <v>112</v>
+        <v>36</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
@@ -2486,7 +2499,7 @@
         <v>140</v>
       </c>
       <c r="N32" s="5" t="s">
-        <v>73</v>
+        <v>200</v>
       </c>
       <c r="O32" s="5" t="s">
         <v>195</v>
@@ -2991,7 +3004,7 @@
         <v>2</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>172</v>
+        <v>198</v>
       </c>
       <c r="K43" s="2" t="s">
         <v>55</v>
@@ -3000,7 +3013,7 @@
         <v>173</v>
       </c>
       <c r="M43" s="2" t="s">
-        <v>73</v>
+        <v>200</v>
       </c>
       <c r="N43" s="2" t="s">
         <v>186</v>

--- a/resultados_torneo.xlsx
+++ b/resultados_torneo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Downloads\preubas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12B5ECB0-66CF-4AC6-8BAB-07EE2CA64939}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52CB07D8-1A6D-4B40-A90C-B81C7C6479A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="623" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="623" uniqueCount="204">
   <si>
     <t>Semana/Fecha</t>
   </si>
@@ -635,6 +635,15 @@
   </si>
   <si>
     <t>maushold_family_of_four</t>
+  </si>
+  <si>
+    <t>Kangaskhan mega</t>
+  </si>
+  <si>
+    <t>Aegislash blade</t>
+  </si>
+  <si>
+    <t>Camerupt mega</t>
   </si>
 </sst>
 </file>
@@ -1647,8 +1656,8 @@
       <c r="K13" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="L13" s="5" t="s">
-        <v>75</v>
+      <c r="L13" s="2" t="s">
+        <v>183</v>
       </c>
       <c r="M13" s="5" t="s">
         <v>76</v>
@@ -2000,7 +2009,7 @@
         <v>191</v>
       </c>
       <c r="L21" s="5" t="s">
-        <v>107</v>
+        <v>202</v>
       </c>
       <c r="M21" s="5" t="s">
         <v>185</v>
@@ -2134,8 +2143,8 @@
       <c r="I24" s="3">
         <v>2</v>
       </c>
-      <c r="J24" s="5" t="s">
-        <v>75</v>
+      <c r="J24" s="2" t="s">
+        <v>183</v>
       </c>
       <c r="K24" s="5" t="s">
         <v>22</v>
@@ -2229,7 +2238,7 @@
         <v>2</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>125</v>
+        <v>201</v>
       </c>
       <c r="K26" s="2" t="s">
         <v>37</v>
@@ -2493,7 +2502,7 @@
         <v>68</v>
       </c>
       <c r="L32" s="5" t="s">
-        <v>139</v>
+        <v>203</v>
       </c>
       <c r="M32" s="5" t="s">
         <v>140</v>
@@ -2628,7 +2637,7 @@
         <v>2</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>150</v>
+        <v>183</v>
       </c>
       <c r="K35" s="2" t="s">
         <v>37</v>
@@ -2769,7 +2778,7 @@
         <v>2</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>155</v>
+        <v>183</v>
       </c>
       <c r="K38" s="2" t="s">
         <v>20</v>
@@ -2866,7 +2875,7 @@
         <v>22</v>
       </c>
       <c r="K40" s="5" t="s">
-        <v>94</v>
+        <v>58</v>
       </c>
       <c r="L40" s="5" t="s">
         <v>190</v>

--- a/resultados_torneo.xlsx
+++ b/resultados_torneo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Downloads\preubas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52CB07D8-1A6D-4B40-A90C-B81C7C6479A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5869E510-5746-4771-A17E-7F085DA79A08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,6 +16,9 @@
     <sheet name="Resultados" sheetId="1" r:id="rId1"/>
     <sheet name="Pokémon Usage" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Pokémon Usage'!$E$1:$E$267</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -32,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="623" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="852" uniqueCount="205">
   <si>
     <t>Semana/Fecha</t>
   </si>
@@ -644,6 +647,9 @@
   </si>
   <si>
     <t>Camerupt mega</t>
+  </si>
+  <si>
+    <t>dada</t>
   </si>
 </sst>
 </file>
@@ -1166,14 +1172,14 @@
       <c r="L2" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="M2" s="2" t="s">
-        <v>23</v>
+      <c r="M2" s="5" t="s">
+        <v>190</v>
       </c>
       <c r="N2" s="2" t="s">
         <v>24</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>25</v>
+        <v>184</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
@@ -1208,7 +1214,7 @@
         <v>27</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>28</v>
+        <v>189</v>
       </c>
       <c r="L3" s="2" t="s">
         <v>29</v>
@@ -1257,8 +1263,8 @@
       <c r="K4" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="L4" s="5" t="s">
-        <v>25</v>
+      <c r="L4" s="2" t="s">
+        <v>184</v>
       </c>
       <c r="M4" s="5" t="s">
         <v>38</v>
@@ -1842,7 +1848,7 @@
         <v>192</v>
       </c>
       <c r="K17" s="5" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="L17" s="5" t="s">
         <v>24</v>
@@ -2883,8 +2889,8 @@
       <c r="M40" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="N40" s="5" t="s">
-        <v>25</v>
+      <c r="N40" s="2" t="s">
+        <v>143</v>
       </c>
       <c r="O40" s="5" t="s">
         <v>21</v>
@@ -3132,582 +3138,1694 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:B71"/>
+  <dimension ref="A1:E267"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
     <col min="2" max="2" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
         <v>180</v>
       </c>
       <c r="B1" s="7" t="s">
         <v>181</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E1" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>22</v>
       </c>
       <c r="B2" s="8">
         <v>22</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E2" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
         <v>25</v>
       </c>
       <c r="B3" s="8">
         <v>18</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E3" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>24</v>
       </c>
       <c r="B4" s="8">
         <v>15</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E4" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>31</v>
       </c>
       <c r="B5" s="8">
         <v>15</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E5" s="2" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
         <v>68</v>
       </c>
       <c r="B6" s="8">
         <v>13</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
         <v>20</v>
       </c>
       <c r="B7" s="8">
         <v>10</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E7" s="2"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
         <v>37</v>
       </c>
       <c r="B8" s="8">
         <v>7</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E8" s="5" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
         <v>38</v>
       </c>
       <c r="B9" s="8">
         <v>6</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E9" s="5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
         <v>39</v>
       </c>
       <c r="B10" s="8">
         <v>6</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E10" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
         <v>55</v>
       </c>
       <c r="B11" s="8">
         <v>6</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E11" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
         <v>91</v>
       </c>
       <c r="B12" s="8">
         <v>6</v>
       </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E12" s="5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
         <v>64</v>
       </c>
       <c r="B13" s="8">
         <v>5</v>
       </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E13" s="5" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
         <v>143</v>
       </c>
       <c r="B14" s="8">
         <v>5</v>
       </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E14" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
         <v>54</v>
       </c>
       <c r="B15" s="8">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E15" s="2" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
         <v>92</v>
       </c>
       <c r="B16" s="8">
         <v>4</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E16" s="5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
         <v>138</v>
       </c>
       <c r="B17" s="8">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E17" s="5" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
         <v>21</v>
       </c>
       <c r="B18" s="8">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E18" s="2"/>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
         <v>23</v>
       </c>
       <c r="B19" s="8">
         <v>3</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E19" s="2"/>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
         <v>29</v>
       </c>
       <c r="B20" s="8">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E20" s="5" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
         <v>66</v>
       </c>
       <c r="B21" s="8">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E21" s="5" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="8" t="s">
         <v>73</v>
       </c>
       <c r="B22" s="8">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E22" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
         <v>105</v>
       </c>
       <c r="B23" s="8">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E23" s="2" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="8" t="s">
         <v>153</v>
       </c>
       <c r="B24" s="8">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E24" s="2" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
         <v>28</v>
       </c>
       <c r="B25" s="8">
         <v>2</v>
       </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E25" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="8" t="s">
         <v>32</v>
       </c>
       <c r="B26" s="8">
         <v>2</v>
       </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E26" s="2" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
         <v>53</v>
       </c>
       <c r="B27" s="8">
         <v>2</v>
       </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E27" s="2" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="8" t="s">
         <v>72</v>
       </c>
       <c r="B28" s="8">
         <v>2</v>
       </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E28" s="5"/>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
         <v>75</v>
       </c>
       <c r="B29" s="8">
         <v>2</v>
       </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E29" s="5"/>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="8" t="s">
         <v>77</v>
       </c>
       <c r="B30" s="8">
         <v>2</v>
       </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E30" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
         <v>83</v>
       </c>
       <c r="B31" s="8">
         <v>2</v>
       </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E31" s="2" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="8" t="s">
         <v>85</v>
       </c>
       <c r="B32" s="8">
         <v>2</v>
       </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E32" s="5" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
         <v>90</v>
       </c>
       <c r="B33" s="8">
         <v>2</v>
       </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E33" s="2" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="8" t="s">
         <v>94</v>
       </c>
       <c r="B34" s="8">
         <v>2</v>
       </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E34" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
         <v>95</v>
       </c>
       <c r="B35" s="8">
         <v>2</v>
       </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E35" s="2" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="8" t="s">
         <v>106</v>
       </c>
       <c r="B36" s="8">
         <v>2</v>
       </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E36" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
         <v>112</v>
       </c>
       <c r="B37" s="8">
         <v>2</v>
       </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E37" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="8" t="s">
         <v>140</v>
       </c>
       <c r="B38" s="8">
         <v>2</v>
       </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E38" s="2" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
         <v>27</v>
       </c>
       <c r="B39" s="8">
         <v>1</v>
       </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E39" s="2" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="8" t="s">
         <v>30</v>
       </c>
       <c r="B40" s="8">
         <v>1</v>
       </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E40" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
         <v>36</v>
       </c>
       <c r="B41" s="8">
         <v>1</v>
       </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E41" s="5" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="8" t="s">
         <v>41</v>
       </c>
       <c r="B42" s="8">
         <v>1</v>
       </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E42" s="2" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
         <v>42</v>
       </c>
       <c r="B43" s="8">
         <v>1</v>
       </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E43" s="2" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="8" t="s">
         <v>56</v>
       </c>
       <c r="B44" s="8">
         <v>1</v>
       </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E44" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
         <v>58</v>
       </c>
       <c r="B45" s="8">
         <v>1</v>
       </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E45" s="2" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="8" t="s">
         <v>67</v>
       </c>
       <c r="B46" s="8">
         <v>1</v>
       </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E46" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
         <v>76</v>
       </c>
       <c r="B47" s="8">
         <v>1</v>
       </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E47" s="2" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="8" t="s">
         <v>82</v>
       </c>
       <c r="B48" s="8">
         <v>1</v>
       </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E48" s="5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
         <v>96</v>
       </c>
       <c r="B49" s="8">
         <v>1</v>
       </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E49" s="5" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="8" t="s">
         <v>107</v>
       </c>
       <c r="B50" s="8">
         <v>1</v>
       </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E50" s="2"/>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
         <v>108</v>
       </c>
       <c r="B51" s="8">
         <v>1</v>
       </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E51" s="2"/>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="8" t="s">
         <v>114</v>
       </c>
       <c r="B52" s="8">
         <v>1</v>
       </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E52" s="5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
         <v>121</v>
       </c>
       <c r="B53" s="8">
         <v>1</v>
       </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E53" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="8" t="s">
         <v>125</v>
       </c>
       <c r="B54" s="8">
         <v>1</v>
       </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E54" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
         <v>127</v>
       </c>
       <c r="B55" s="8">
         <v>1</v>
       </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E55" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="8" t="s">
         <v>139</v>
       </c>
       <c r="B56" s="8">
         <v>1</v>
       </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E56" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
         <v>141</v>
       </c>
       <c r="B57" s="8">
         <v>1</v>
       </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E57" s="5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="8" t="s">
         <v>150</v>
       </c>
       <c r="B58" s="8">
         <v>1</v>
       </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E58" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
         <v>155</v>
       </c>
       <c r="B59" s="8">
         <v>1</v>
       </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E59" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="8" t="s">
         <v>156</v>
       </c>
       <c r="B60" s="8">
         <v>1</v>
       </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E60" s="5" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
         <v>158</v>
       </c>
       <c r="B61" s="8">
         <v>1</v>
       </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E61" s="5" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="8" t="s">
         <v>159</v>
       </c>
       <c r="B62" s="8">
         <v>1</v>
       </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E62" s="2"/>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
         <v>160</v>
       </c>
       <c r="B63" s="8">
         <v>1</v>
       </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E63" s="2"/>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="8" t="s">
         <v>166</v>
       </c>
       <c r="B64" s="8">
         <v>1</v>
       </c>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E64" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
         <v>167</v>
       </c>
       <c r="B65" s="8">
         <v>1</v>
       </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E65" s="5" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="8" t="s">
         <v>169</v>
       </c>
       <c r="B66" s="8">
         <v>1</v>
       </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E66" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
         <v>170</v>
       </c>
       <c r="B67" s="8">
         <v>1</v>
       </c>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E67" s="2" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" s="8" t="s">
         <v>172</v>
       </c>
       <c r="B68" s="8">
         <v>1</v>
       </c>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E68" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
         <v>173</v>
       </c>
       <c r="B69" s="8">
         <v>1</v>
       </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E69" s="5" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" s="8" t="s">
         <v>174</v>
       </c>
       <c r="B70" s="8">
         <v>1</v>
       </c>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E70" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
         <v>179</v>
       </c>
       <c r="B71" s="8">
         <v>1</v>
       </c>
+      <c r="E71" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E72" s="5"/>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E73" s="5"/>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E74" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E75" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E76" s="5" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E77" s="5" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E78" s="2" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E79" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E80" s="5" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="81" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E81" s="5" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="82" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E82" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="83" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E83" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="84" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E84" s="5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="85" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E85" s="5" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="86" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E86" s="2" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="87" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E87" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="88" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E88" s="2" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="89" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E89" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="90" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E90" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="91" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E91" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="92" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E92" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="93" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E93" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="94" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E94" s="2"/>
+    </row>
+    <row r="95" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E95" s="2"/>
+    </row>
+    <row r="96" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E96" s="5" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="97" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E97" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="98" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E98" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="99" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E99" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="100" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E100" s="5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="101" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E101" s="2" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="102" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E102" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="103" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E103" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="104" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E104" s="2" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="105" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E105" s="5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="106" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E106" s="2"/>
+    </row>
+    <row r="107" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E107" s="2"/>
+    </row>
+    <row r="108" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E108" s="5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="109" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E109" s="5" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="110" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E110" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="111" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E111" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="112" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E112" s="5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="113" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E113" s="5" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="114" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E114" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="115" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E115" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="116" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E116" s="5"/>
+    </row>
+    <row r="117" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E117" s="5"/>
+    </row>
+    <row r="118" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E118" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="119" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E119" s="5" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="120" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E120" s="5" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="121" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E121" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="122" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E122" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="123" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E123" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="124" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E124" s="5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="125" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E125" s="5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="126" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E126" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="127" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E127" s="2" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="128" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E128" s="5" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="129" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E129" s="5" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="130" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E130" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="131" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E131" s="2" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="132" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E132" s="5" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="133" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E133" s="5" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="134" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E134" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="135" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E135" s="5" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="136" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E136" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="137" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E137" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="138" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E138" s="2"/>
+    </row>
+    <row r="139" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E139" s="2"/>
+    </row>
+    <row r="140" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E140" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="141" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E141" s="5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="142" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E142" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="143" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E143" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="144" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E144" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="145" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E145" s="5" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="146" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E146" s="2" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="147" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E147" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="148" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E148" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="149" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E149" s="5" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="150" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E150" s="2"/>
+    </row>
+    <row r="151" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E151" s="2"/>
+    </row>
+    <row r="152" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E152" s="5" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="153" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E153" s="5" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="154" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E154" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="155" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E155" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="156" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E156" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="157" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E157" s="5" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="158" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E158" s="5" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="159" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E159" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="160" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E160" s="5"/>
+    </row>
+    <row r="161" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E161" s="5"/>
+    </row>
+    <row r="162" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E162" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="163" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E163" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="164" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E164" s="5" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="165" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E165" s="5" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="166" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E166" s="5" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="167" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E167" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="168" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E168" s="5" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="169" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E169" s="5" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="170" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E170" s="2" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="171" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E171" s="2" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="172" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E172" s="5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="173" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E173" s="5" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="174" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E174" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="175" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E175" s="2" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="176" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E176" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="177" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E177" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="178" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E178" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="179" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E179" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="180" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E180" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="181" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E181" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="182" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E182" s="2"/>
+    </row>
+    <row r="183" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E183" s="2"/>
+    </row>
+    <row r="184" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E184" s="5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="185" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E185" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="186" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E186" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="187" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E187" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="188" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E188" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="189" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E189" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="190" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E190" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="191" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E191" s="2" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="192" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E192" s="5" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="193" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E193" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="194" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E194" s="2"/>
+    </row>
+    <row r="195" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E195" s="2"/>
+    </row>
+    <row r="196" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E196" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="197" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E197" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="198" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E198" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="199" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E199" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="200" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E200" s="5" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="201" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E201" s="5" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="202" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E202" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="203" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E203" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="204" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E204" s="5"/>
+    </row>
+    <row r="205" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E205" s="5"/>
+    </row>
+    <row r="206" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E206" s="2" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="207" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E207" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="208" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E208" s="5" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="209" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E209" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="210" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E210" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="211" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E211" s="5" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="212" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E212" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="213" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E213" s="5" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="214" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E214" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="215" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E215" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="216" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E216" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="217" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E217" s="5" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="218" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E218" s="2" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="219" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E219" s="2" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="220" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E220" s="5" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="221" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E221" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="224" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E224" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="225" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E225" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="226" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E226" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="227" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E227" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="228" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E228" s="2"/>
+    </row>
+    <row r="229" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E229" s="2"/>
+    </row>
+    <row r="230" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E230" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="231" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E231" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="232" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E232" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="233" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E233" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="234" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E234" s="5" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="235" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E235" s="5" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="236" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E236" s="5" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="237" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E237" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="238" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E238" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="239" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E239" s="5" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="240" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E240" s="2"/>
+    </row>
+    <row r="241" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E241" s="2"/>
+    </row>
+    <row r="242" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E242" s="5" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="243" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E243" s="5" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="244" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E244" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="245" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E245" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="246" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E246" s="5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="247" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E247" s="5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="248" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E248" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="249" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E249" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="250" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E250" s="5"/>
+    </row>
+    <row r="251" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E251" s="5"/>
+    </row>
+    <row r="252" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E252" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="253" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E253" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="254" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E254" s="5" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="255" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E255" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="256" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E256" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="257" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E257" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="258" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E258" s="5" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="259" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E259" s="5" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="260" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E260" s="2" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="261" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E261" s="2" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="262" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E262" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="263" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E263" s="5" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="264" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E264" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="265" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E265" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="266" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E266" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="267" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E267" s="5" t="s">
+        <v>143</v>
+      </c>
     </row>
   </sheetData>
+  <autoFilter ref="E1:E267" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/resultados_torneo.xlsx
+++ b/resultados_torneo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Downloads\preubas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6882EC35-2BC7-4439-9D6E-68A581E0FED2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86AB9ED6-8845-4668-927C-7B492E66B820}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Resultados" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="16" r:id="rId5"/>
+    <pivotCache cacheId="0" r:id="rId5"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="658" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="658" uniqueCount="170">
   <si>
     <t>Semana/Fecha</t>
   </si>
@@ -499,9 +499,6 @@
   </si>
   <si>
     <t>Tyranitar Mega</t>
-  </si>
-  <si>
-    <t>Gardevoir mega</t>
   </si>
   <si>
     <t>Scovillan mega</t>
@@ -1569,7 +1566,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{63FAC1E4-48DE-47B8-8A9B-F039882C55D7}" name="TablaDinámica2" cacheId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{63FAC1E4-48DE-47B8-8A9B-F039882C55D7}" name="TablaDinámica2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:B56" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="1">
     <pivotField axis="axisRow" dataField="1" showAll="0">
@@ -2196,7 +2193,7 @@
         <v>22</v>
       </c>
       <c r="M2" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="N2" s="2" t="s">
         <v>23</v>
@@ -2236,14 +2233,14 @@
       <c r="J3" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="K3" s="2" t="s">
-        <v>153</v>
+      <c r="K3" s="5" t="s">
+        <v>155</v>
       </c>
       <c r="L3" s="2" t="s">
         <v>27</v>
       </c>
       <c r="M3" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="N3" s="2" t="s">
         <v>28</v>
@@ -2445,7 +2442,7 @@
         <v>2</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="K8" s="5" t="s">
         <v>48</v>
@@ -2495,7 +2492,7 @@
         <v>52</v>
       </c>
       <c r="K9" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="L9" s="5" t="s">
         <v>21</v>
@@ -2633,7 +2630,7 @@
         <v>2</v>
       </c>
       <c r="J12" s="5" t="s">
-        <v>26</v>
+        <v>155</v>
       </c>
       <c r="K12" s="5" t="s">
         <v>28</v>
@@ -2648,7 +2645,7 @@
         <v>22</v>
       </c>
       <c r="O12" s="5" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
@@ -2773,8 +2770,8 @@
       <c r="I15" s="3">
         <v>2</v>
       </c>
-      <c r="J15" s="2" t="s">
-        <v>156</v>
+      <c r="J15" s="5" t="s">
+        <v>155</v>
       </c>
       <c r="K15" s="2" t="s">
         <v>23</v>
@@ -2824,7 +2821,7 @@
         <v>79</v>
       </c>
       <c r="K16" s="5" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="L16" s="2" t="s">
         <v>149</v>
@@ -2871,7 +2868,7 @@
         <v>52</v>
       </c>
       <c r="K17" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="L17" s="5" t="s">
         <v>23</v>
@@ -3032,13 +3029,13 @@
         <v>2</v>
       </c>
       <c r="J21" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="K21" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="L21" s="5" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="M21" s="5" t="s">
         <v>150</v>
@@ -3129,7 +3126,7 @@
         <v>149</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="L23" s="2" t="s">
         <v>20</v>
@@ -3226,7 +3223,7 @@
         <v>150</v>
       </c>
       <c r="L25" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="M25" s="5" t="s">
         <v>58</v>
@@ -3267,7 +3264,7 @@
         <v>2</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="K26" s="2" t="s">
         <v>34</v>
@@ -3320,7 +3317,7 @@
         <v>23</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="M27" s="2" t="s">
         <v>22</v>
@@ -3531,16 +3528,16 @@
         <v>62</v>
       </c>
       <c r="L32" s="5" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="M32" s="5" t="s">
         <v>115</v>
       </c>
       <c r="N32" s="5" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="O32" s="5" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
@@ -3722,7 +3719,7 @@
         <v>23</v>
       </c>
       <c r="M36" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="N36" s="5" t="s">
         <v>29</v>
@@ -3907,7 +3904,7 @@
         <v>52</v>
       </c>
       <c r="L40" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="M40" s="5" t="s">
         <v>23</v>
@@ -3954,7 +3951,7 @@
         <v>114</v>
       </c>
       <c r="L41" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="M41" s="5" t="s">
         <v>126</v>
@@ -3997,8 +3994,8 @@
       <c r="J42" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="K42" s="2" t="s">
-        <v>153</v>
+      <c r="K42" s="5" t="s">
+        <v>155</v>
       </c>
       <c r="L42" s="2" t="s">
         <v>62</v>
@@ -4042,7 +4039,7 @@
         <v>2</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="K43" s="2" t="s">
         <v>49</v>
@@ -4051,10 +4048,10 @@
         <v>140</v>
       </c>
       <c r="M43" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="N43" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="O43" s="2" t="s">
         <v>62</v>
@@ -4161,6 +4158,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:B64"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -4176,7 +4174,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>117</v>
       </c>
@@ -4184,7 +4182,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>22</v>
       </c>
@@ -4192,7 +4190,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>28</v>
       </c>
@@ -4200,7 +4198,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>23</v>
       </c>
@@ -4208,7 +4206,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>62</v>
       </c>
@@ -4216,7 +4214,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>149</v>
       </c>
@@ -4224,7 +4222,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>20</v>
       </c>
@@ -4232,7 +4230,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>114</v>
       </c>
@@ -4240,7 +4238,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>34</v>
       </c>
@@ -4248,7 +4246,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>49</v>
       </c>
@@ -4256,7 +4254,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>36</v>
       </c>
@@ -4264,7 +4262,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>35</v>
       </c>
@@ -4272,7 +4270,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>58</v>
       </c>
@@ -4280,15 +4278,15 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B15">
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>48</v>
       </c>
@@ -4296,15 +4294,15 @@
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B17">
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>33</v>
       </c>
@@ -4312,7 +4310,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>21</v>
       </c>
@@ -4320,7 +4318,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>52</v>
       </c>
@@ -4328,7 +4326,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>126</v>
       </c>
@@ -4338,21 +4336,21 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B22">
         <v>3</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B23">
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>150</v>
       </c>
@@ -4360,15 +4358,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B25">
         <v>3</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>27</v>
       </c>
@@ -4376,7 +4374,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>60</v>
       </c>
@@ -4384,7 +4382,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>29</v>
       </c>
@@ -4392,7 +4390,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>69</v>
       </c>
@@ -4400,7 +4398,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>115</v>
       </c>
@@ -4408,7 +4406,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>66</v>
       </c>
@@ -4416,15 +4414,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B32">
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>79</v>
       </c>
@@ -4432,15 +4430,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B34">
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>25</v>
       </c>
@@ -4448,7 +4446,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>145</v>
       </c>
@@ -4456,7 +4454,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>129</v>
       </c>
@@ -4464,15 +4462,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B38">
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>68</v>
       </c>
@@ -4480,15 +4478,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B40">
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>151</v>
       </c>
@@ -4504,7 +4502,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>140</v>
       </c>
@@ -4512,23 +4510,23 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B44">
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B45">
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>130</v>
       </c>
@@ -4536,7 +4534,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>50</v>
       </c>
@@ -4544,7 +4542,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>61</v>
       </c>
@@ -4552,7 +4550,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>131</v>
       </c>
@@ -4560,7 +4558,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>138</v>
       </c>
@@ -4568,7 +4566,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>152</v>
       </c>
@@ -4576,52 +4574,61 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:2" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="53" spans="1:2" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="54" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" s="8"/>
       <c r="B54" s="8"/>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" s="8"/>
       <c r="B55" s="8"/>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" s="8"/>
       <c r="B56" s="8"/>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" s="8"/>
       <c r="B57" s="8"/>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" s="8"/>
       <c r="B58" s="8"/>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" s="8"/>
       <c r="B59" s="8"/>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" s="8"/>
       <c r="B60" s="8"/>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" s="8"/>
       <c r="B61" s="8"/>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" s="8"/>
       <c r="B62" s="8"/>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" s="8"/>
       <c r="B63" s="8"/>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" s="8"/>
       <c r="B64" s="8"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B64" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
+  <autoFilter ref="A1:B64" xr:uid="{00000000-0001-0000-0100-000000000000}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="Gardevoir"/>
+        <filter val="Gardevoir Mega"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B64">
     <sortCondition descending="1" ref="B2:B64"/>
   </sortState>
@@ -4640,15 +4647,15 @@
   <sheetData>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B4" s="11">
         <v>1</v>
@@ -4712,7 +4719,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B12" s="11">
         <v>1</v>
@@ -4776,7 +4783,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="10" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B20" s="11">
         <v>1</v>
@@ -4808,7 +4815,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B24" s="11">
         <v>3</v>
@@ -4816,7 +4823,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="10" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B25" s="11">
         <v>4</v>
@@ -4872,7 +4879,7 @@
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="10" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B32" s="11">
         <v>3</v>
@@ -4880,7 +4887,7 @@
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="10" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B33" s="11">
         <v>1</v>
@@ -4896,7 +4903,7 @@
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" s="10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B35" s="11">
         <v>1</v>
@@ -4920,7 +4927,7 @@
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" s="10" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B38" s="11">
         <v>3</v>
@@ -4944,7 +4951,7 @@
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" s="10" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B41" s="11">
         <v>5</v>
@@ -5032,7 +5039,7 @@
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" s="10" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B52" s="11">
         <v>2</v>
@@ -5048,7 +5055,7 @@
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" s="10" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B54" s="11"/>
     </row>
@@ -5062,7 +5069,7 @@
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" s="10" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B56" s="11">
         <v>264</v>
@@ -5107,7 +5114,7 @@
   <sheetData>
     <row r="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="2" spans="2:2" x14ac:dyDescent="0.25">
@@ -5173,7 +5180,7 @@
     <row r="12" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B12" s="2" t="str">
         <f>Resultados!J12</f>
-        <v>Gardevoir</v>
+        <v>Gardevoir Mega</v>
       </c>
     </row>
     <row r="13" spans="2:2" x14ac:dyDescent="0.25">
@@ -5383,7 +5390,7 @@
     <row r="47" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B47" s="2" t="str">
         <f>Resultados!K3</f>
-        <v>Gardevoir mega</v>
+        <v>Gardevoir Mega</v>
       </c>
     </row>
     <row r="48" spans="2:2" x14ac:dyDescent="0.25">
@@ -5617,7 +5624,7 @@
     <row r="86" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B86" s="2" t="str">
         <f>Resultados!K42</f>
-        <v>Gardevoir mega</v>
+        <v>Gardevoir Mega</v>
       </c>
     </row>
     <row r="87" spans="2:2" x14ac:dyDescent="0.25">

--- a/resultados_torneo.xlsx
+++ b/resultados_torneo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Downloads\preubas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86AB9ED6-8845-4668-927C-7B492E66B820}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79DAF344-56AE-45C5-A0E1-88C1A1B8EBC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="658" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="658" uniqueCount="171">
   <si>
     <t>Semana/Fecha</t>
   </si>
@@ -550,6 +550,9 @@
   </si>
   <si>
     <t>Gengar mega</t>
+  </si>
+  <si>
+    <t>Kommo_o</t>
   </si>
 </sst>
 </file>
@@ -2187,7 +2190,7 @@
         <v>20</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>21</v>
+        <v>170</v>
       </c>
       <c r="L2" s="2" t="s">
         <v>22</v>
@@ -4158,7 +4161,6 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:B64"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -4174,7 +4176,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="2" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>117</v>
       </c>
@@ -4182,7 +4184,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>22</v>
       </c>
@@ -4190,7 +4192,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>28</v>
       </c>
@@ -4198,7 +4200,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>23</v>
       </c>
@@ -4206,7 +4208,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>62</v>
       </c>
@@ -4214,7 +4216,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>149</v>
       </c>
@@ -4222,7 +4224,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>20</v>
       </c>
@@ -4230,7 +4232,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>114</v>
       </c>
@@ -4238,7 +4240,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>34</v>
       </c>
@@ -4246,7 +4248,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>49</v>
       </c>
@@ -4254,7 +4256,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>36</v>
       </c>
@@ -4262,7 +4264,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="13" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>35</v>
       </c>
@@ -4270,7 +4272,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="14" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>58</v>
       </c>
@@ -4278,7 +4280,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>153</v>
       </c>
@@ -4286,7 +4288,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>48</v>
       </c>
@@ -4294,7 +4296,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>169</v>
       </c>
@@ -4302,7 +4304,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>33</v>
       </c>
@@ -4310,7 +4312,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>21</v>
       </c>
@@ -4318,7 +4320,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>52</v>
       </c>
@@ -4326,7 +4328,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>126</v>
       </c>
@@ -4342,7 +4344,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="23" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>160</v>
       </c>
@@ -4350,7 +4352,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>150</v>
       </c>
@@ -4358,7 +4360,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>154</v>
       </c>
@@ -4366,7 +4368,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="26" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>27</v>
       </c>
@@ -4374,7 +4376,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>60</v>
       </c>
@@ -4382,7 +4384,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>29</v>
       </c>
@@ -4390,7 +4392,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>69</v>
       </c>
@@ -4398,7 +4400,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>115</v>
       </c>
@@ -4406,7 +4408,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>66</v>
       </c>
@@ -4414,7 +4416,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>156</v>
       </c>
@@ -4422,7 +4424,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>79</v>
       </c>
@@ -4430,7 +4432,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="34" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>162</v>
       </c>
@@ -4438,7 +4440,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>25</v>
       </c>
@@ -4446,7 +4448,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>145</v>
       </c>
@@ -4454,7 +4456,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>129</v>
       </c>
@@ -4462,7 +4464,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>163</v>
       </c>
@@ -4470,7 +4472,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>68</v>
       </c>
@@ -4478,7 +4480,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>159</v>
       </c>
@@ -4486,7 +4488,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>151</v>
       </c>
@@ -4502,7 +4504,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>140</v>
       </c>
@@ -4510,7 +4512,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>157</v>
       </c>
@@ -4518,7 +4520,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>158</v>
       </c>
@@ -4526,7 +4528,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>130</v>
       </c>
@@ -4534,7 +4536,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>50</v>
       </c>
@@ -4542,7 +4544,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>61</v>
       </c>
@@ -4550,7 +4552,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>131</v>
       </c>
@@ -4558,7 +4560,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>138</v>
       </c>
@@ -4566,7 +4568,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>152</v>
       </c>
@@ -4574,61 +4576,52 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:2" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="53" spans="1:2" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="54" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" s="8"/>
       <c r="B54" s="8"/>
     </row>
-    <row r="55" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" s="8"/>
       <c r="B55" s="8"/>
     </row>
-    <row r="56" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" s="8"/>
       <c r="B56" s="8"/>
     </row>
-    <row r="57" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" s="8"/>
       <c r="B57" s="8"/>
     </row>
-    <row r="58" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" s="8"/>
       <c r="B58" s="8"/>
     </row>
-    <row r="59" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" s="8"/>
       <c r="B59" s="8"/>
     </row>
-    <row r="60" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" s="8"/>
       <c r="B60" s="8"/>
     </row>
-    <row r="61" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" s="8"/>
       <c r="B61" s="8"/>
     </row>
-    <row r="62" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" s="8"/>
       <c r="B62" s="8"/>
     </row>
-    <row r="63" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" s="8"/>
       <c r="B63" s="8"/>
     </row>
-    <row r="64" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" s="8"/>
       <c r="B64" s="8"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B64" xr:uid="{00000000-0001-0000-0100-000000000000}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="Gardevoir"/>
-        <filter val="Gardevoir Mega"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:B64" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B64">
     <sortCondition descending="1" ref="B2:B64"/>
   </sortState>
@@ -5384,7 +5377,7 @@
     <row r="46" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B46" s="2" t="str">
         <f>Resultados!K2</f>
-        <v>Kommo-o</v>
+        <v>Kommo_o</v>
       </c>
     </row>
     <row r="47" spans="2:2" x14ac:dyDescent="0.25">

--- a/resultados_torneo.xlsx
+++ b/resultados_torneo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Downloads\preubas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79DAF344-56AE-45C5-A0E1-88C1A1B8EBC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78F2EF32-4CD4-4CDE-AE02-C2D1AC7E5322}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Resultados" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId5"/>
+    <pivotCache cacheId="3" r:id="rId5"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="658" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="657" uniqueCount="170">
   <si>
     <t>Semana/Fecha</t>
   </si>
@@ -120,9 +120,6 @@
     <t>Arcanine</t>
   </si>
   <si>
-    <t>Gardevoir</t>
-  </si>
-  <si>
     <t>Tyranitar</t>
   </si>
   <si>
@@ -552,7 +549,7 @@
     <t>Gengar mega</t>
   </si>
   <si>
-    <t>Kommo_o</t>
+    <t>kommo</t>
   </si>
 </sst>
 </file>
@@ -698,7 +695,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Usuario" refreshedDate="46154.692237731484" createdVersion="7" refreshedVersion="7" minRefreshableVersion="3" recordCount="265" xr:uid="{4C8922C4-D533-4821-ABBF-859C40984883}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Usuario" refreshedDate="46154.700821759259" createdVersion="7" refreshedVersion="7" minRefreshableVersion="3" recordCount="265" xr:uid="{4C8922C4-D533-4821-ABBF-859C40984883}">
   <cacheSource type="worksheet">
     <worksheetSource ref="B1:B1048576" sheet="dinamica"/>
   </cacheSource>
@@ -714,10 +711,9 @@
         <s v="Aerodactyl Mega"/>
         <s v="Pelipper"/>
         <s v="Venusaur"/>
-        <s v="Gardevoir"/>
+        <s v="Gardevoir Mega"/>
         <s v="Incineroar"/>
         <s v="Talonflame"/>
-        <s v="Gardevoir Mega"/>
         <s v="Whimsicott"/>
         <s v="Floette-Eternal"/>
         <s v="Gengar mega"/>
@@ -729,7 +725,7 @@
         <s v="Tyranitar Mega"/>
         <s v="Typhlosion Hisui"/>
         <s v="palafin_hero"/>
-        <s v="Kommo-o"/>
+        <s v="kommo"/>
         <s v="Archaludon"/>
         <s v="Scovillan mega"/>
         <s v="Basculegion-Male"/>
@@ -740,6 +736,7 @@
         <s v="Torkoal"/>
         <s v="Froslass Mega"/>
         <s v="Excadrill"/>
+        <s v="Kommo-o"/>
         <s v="Dragonite"/>
         <s v="Aegislash blade"/>
         <s v="Sylveon"/>
@@ -810,757 +807,757 @@
     <x v="11"/>
   </r>
   <r>
+    <x v="9"/>
+  </r>
+  <r>
     <x v="12"/>
   </r>
   <r>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
     <x v="13"/>
   </r>
   <r>
+    <x v="14"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="15"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="16"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="17"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="13"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="18"/>
+  </r>
+  <r>
+    <x v="18"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="19"/>
+  </r>
+  <r>
+    <x v="15"/>
+  </r>
+  <r>
+    <x v="20"/>
+  </r>
+  <r>
+    <x v="21"/>
+  </r>
+  <r>
+    <x v="22"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="23"/>
+  </r>
+  <r>
+    <x v="9"/>
+  </r>
+  <r>
+    <x v="17"/>
+  </r>
+  <r>
+    <x v="13"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="24"/>
+  </r>
+  <r>
+    <x v="25"/>
+  </r>
+  <r>
+    <x v="26"/>
+  </r>
+  <r>
+    <x v="27"/>
+  </r>
+  <r>
+    <x v="28"/>
+  </r>
+  <r>
+    <x v="17"/>
+  </r>
+  <r>
+    <x v="28"/>
+  </r>
+  <r>
+    <x v="29"/>
+  </r>
+  <r>
+    <x v="5"/>
+  </r>
+  <r>
+    <x v="25"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="30"/>
+  </r>
+  <r>
+    <x v="31"/>
+  </r>
+  <r>
+    <x v="32"/>
+  </r>
+  <r>
+    <x v="15"/>
+  </r>
+  <r>
+    <x v="16"/>
+  </r>
+  <r>
+    <x v="17"/>
+  </r>
+  <r>
+    <x v="29"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="31"/>
+  </r>
+  <r>
+    <x v="29"/>
+  </r>
+  <r>
+    <x v="10"/>
+  </r>
+  <r>
+    <x v="13"/>
+  </r>
+  <r>
+    <x v="13"/>
+  </r>
+  <r>
+    <x v="17"/>
+  </r>
+  <r>
+    <x v="33"/>
+  </r>
+  <r>
+    <x v="33"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="7"/>
+  </r>
+  <r>
     <x v="6"/>
   </r>
   <r>
+    <x v="13"/>
+  </r>
+  <r>
+    <x v="9"/>
+  </r>
+  <r>
+    <x v="7"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="15"/>
+  </r>
+  <r>
+    <x v="18"/>
+  </r>
+  <r>
+    <x v="26"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
     <x v="4"/>
   </r>
   <r>
     <x v="4"/>
   </r>
   <r>
+    <x v="7"/>
+  </r>
+  <r>
+    <x v="34"/>
+  </r>
+  <r>
+    <x v="35"/>
+  </r>
+  <r>
+    <x v="7"/>
+  </r>
+  <r>
+    <x v="11"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="29"/>
+  </r>
+  <r>
+    <x v="7"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="29"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="29"/>
+  </r>
+  <r>
+    <x v="36"/>
+  </r>
+  <r>
+    <x v="17"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="29"/>
+  </r>
+  <r>
     <x v="14"/>
   </r>
   <r>
+    <x v="31"/>
+  </r>
+  <r>
+    <x v="14"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="37"/>
+  </r>
+  <r>
+    <x v="26"/>
+  </r>
+  <r>
+    <x v="38"/>
+  </r>
+  <r>
     <x v="15"/>
   </r>
   <r>
+    <x v="28"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="29"/>
+  </r>
+  <r>
+    <x v="29"/>
+  </r>
+  <r>
+    <x v="15"/>
+  </r>
+  <r>
+    <x v="39"/>
+  </r>
+  <r>
+    <x v="25"/>
+  </r>
+  <r>
+    <x v="30"/>
+  </r>
+  <r>
+    <x v="10"/>
+  </r>
+  <r>
+    <x v="40"/>
+  </r>
+  <r>
+    <x v="26"/>
+  </r>
+  <r>
+    <x v="41"/>
+  </r>
+  <r>
+    <x v="25"/>
+  </r>
+  <r>
+    <x v="30"/>
+  </r>
+  <r>
+    <x v="31"/>
+  </r>
+  <r>
+    <x v="28"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="26"/>
+  </r>
+  <r>
+    <x v="29"/>
+  </r>
+  <r>
+    <x v="15"/>
+  </r>
+  <r>
+    <x v="26"/>
+  </r>
+  <r>
+    <x v="26"/>
+  </r>
+  <r>
+    <x v="42"/>
+  </r>
+  <r>
+    <x v="26"/>
+  </r>
+  <r>
+    <x v="10"/>
+  </r>
+  <r>
+    <x v="28"/>
+  </r>
+  <r>
+    <x v="26"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="10"/>
+  </r>
+  <r>
+    <x v="16"/>
+  </r>
+  <r>
+    <x v="43"/>
+  </r>
+  <r>
+    <x v="26"/>
+  </r>
+  <r>
+    <x v="28"/>
+  </r>
+  <r>
+    <x v="35"/>
+  </r>
+  <r>
+    <x v="26"/>
+  </r>
+  <r>
+    <x v="15"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="15"/>
+  </r>
+  <r>
+    <x v="10"/>
+  </r>
+  <r>
+    <x v="44"/>
+  </r>
+  <r>
+    <x v="26"/>
+  </r>
+  <r>
+    <x v="26"/>
+  </r>
+  <r>
+    <x v="37"/>
+  </r>
+  <r>
+    <x v="25"/>
+  </r>
+  <r>
+    <x v="10"/>
+  </r>
+  <r>
+    <x v="13"/>
+  </r>
+  <r>
+    <x v="45"/>
+  </r>
+  <r>
+    <x v="29"/>
+  </r>
+  <r>
+    <x v="33"/>
+  </r>
+  <r>
+    <x v="17"/>
+  </r>
+  <r>
+    <x v="46"/>
+  </r>
+  <r>
+    <x v="28"/>
+  </r>
+  <r>
+    <x v="28"/>
+  </r>
+  <r>
+    <x v="29"/>
+  </r>
+  <r>
+    <x v="28"/>
+  </r>
+  <r>
+    <x v="15"/>
+  </r>
+  <r>
+    <x v="15"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="47"/>
+  </r>
+  <r>
+    <x v="15"/>
+  </r>
+  <r>
+    <x v="29"/>
+  </r>
+  <r>
+    <x v="24"/>
+  </r>
+  <r>
+    <x v="15"/>
+  </r>
+  <r>
+    <x v="31"/>
+  </r>
+  <r>
+    <x v="15"/>
+  </r>
+  <r>
+    <x v="26"/>
+  </r>
+  <r>
+    <x v="26"/>
+  </r>
+  <r>
+    <x v="15"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="28"/>
+  </r>
+  <r>
+    <x v="28"/>
+  </r>
+  <r>
+    <x v="15"/>
+  </r>
+  <r>
+    <x v="15"/>
+  </r>
+  <r>
+    <x v="26"/>
+  </r>
+  <r>
+    <x v="10"/>
+  </r>
+  <r>
+    <x v="15"/>
+  </r>
+  <r>
+    <x v="10"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="26"/>
+  </r>
+  <r>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="46"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="29"/>
+  </r>
+  <r>
+    <x v="26"/>
+  </r>
+  <r>
+    <x v="48"/>
+  </r>
+  <r>
+    <x v="26"/>
+  </r>
+  <r>
+    <x v="28"/>
+  </r>
+  <r>
+    <x v="24"/>
+  </r>
+  <r>
+    <x v="26"/>
+  </r>
+  <r>
+    <x v="10"/>
+  </r>
+  <r>
+    <x v="49"/>
+  </r>
+  <r>
+    <x v="14"/>
+  </r>
+  <r>
+    <x v="13"/>
+  </r>
+  <r>
+    <x v="37"/>
+  </r>
+  <r>
+    <x v="26"/>
+  </r>
+  <r>
+    <x v="48"/>
+  </r>
+  <r>
+    <x v="37"/>
+  </r>
+  <r>
+    <x v="26"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="15"/>
+  </r>
+  <r>
+    <x v="37"/>
+  </r>
+  <r>
+    <x v="24"/>
+  </r>
+  <r>
+    <x v="10"/>
+  </r>
+  <r>
+    <x v="46"/>
+  </r>
+  <r>
+    <x v="43"/>
+  </r>
+  <r>
+    <x v="13"/>
+  </r>
+  <r>
+    <x v="15"/>
+  </r>
+  <r>
+    <x v="15"/>
+  </r>
+  <r>
+    <x v="34"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="26"/>
+  </r>
+  <r>
+    <x v="10"/>
+  </r>
+  <r>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="35"/>
+  </r>
+  <r>
+    <x v="12"/>
+  </r>
+  <r>
+    <x v="29"/>
+  </r>
+  <r>
+    <x v="37"/>
+  </r>
+  <r>
+    <x v="35"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
     <x v="2"/>
   </r>
   <r>
-    <x v="3"/>
-  </r>
-  <r>
-    <x v="3"/>
-  </r>
-  <r>
-    <x v="16"/>
-  </r>
-  <r>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="17"/>
-  </r>
-  <r>
-    <x v="4"/>
-  </r>
-  <r>
-    <x v="4"/>
-  </r>
-  <r>
-    <x v="18"/>
-  </r>
-  <r>
-    <x v="3"/>
-  </r>
-  <r>
-    <x v="14"/>
-  </r>
-  <r>
-    <x v="3"/>
-  </r>
-  <r>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="3"/>
-  </r>
-  <r>
-    <x v="19"/>
-  </r>
-  <r>
-    <x v="19"/>
-  </r>
-  <r>
-    <x v="3"/>
-  </r>
-  <r>
-    <x v="20"/>
-  </r>
-  <r>
-    <x v="16"/>
-  </r>
-  <r>
-    <x v="21"/>
-  </r>
-  <r>
-    <x v="22"/>
-  </r>
-  <r>
-    <x v="23"/>
-  </r>
-  <r>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="3"/>
-  </r>
-  <r>
-    <x v="24"/>
-  </r>
-  <r>
-    <x v="12"/>
-  </r>
-  <r>
-    <x v="18"/>
-  </r>
-  <r>
-    <x v="14"/>
-  </r>
-  <r>
-    <x v="4"/>
-  </r>
-  <r>
-    <x v="4"/>
-  </r>
-  <r>
-    <x v="25"/>
+    <x v="28"/>
+  </r>
+  <r>
+    <x v="50"/>
+  </r>
+  <r>
+    <x v="28"/>
+  </r>
+  <r>
+    <x v="15"/>
+  </r>
+  <r>
+    <x v="28"/>
   </r>
   <r>
     <x v="26"/>
   </r>
   <r>
-    <x v="27"/>
-  </r>
-  <r>
-    <x v="28"/>
-  </r>
-  <r>
-    <x v="29"/>
-  </r>
-  <r>
-    <x v="18"/>
-  </r>
-  <r>
-    <x v="29"/>
-  </r>
-  <r>
-    <x v="30"/>
-  </r>
-  <r>
-    <x v="5"/>
+    <x v="35"/>
   </r>
   <r>
     <x v="26"/>
   </r>
   <r>
-    <x v="4"/>
-  </r>
-  <r>
-    <x v="4"/>
-  </r>
-  <r>
-    <x v="0"/>
+    <x v="26"/>
+  </r>
+  <r>
+    <x v="34"/>
+  </r>
+  <r>
+    <x v="44"/>
   </r>
   <r>
     <x v="31"/>
   </r>
   <r>
-    <x v="32"/>
-  </r>
-  <r>
-    <x v="33"/>
-  </r>
-  <r>
-    <x v="16"/>
-  </r>
-  <r>
-    <x v="17"/>
-  </r>
-  <r>
-    <x v="18"/>
-  </r>
-  <r>
-    <x v="30"/>
-  </r>
-  <r>
-    <x v="4"/>
-  </r>
-  <r>
-    <x v="4"/>
-  </r>
-  <r>
-    <x v="32"/>
-  </r>
-  <r>
-    <x v="30"/>
-  </r>
-  <r>
     <x v="10"/>
   </r>
   <r>
-    <x v="14"/>
-  </r>
-  <r>
-    <x v="14"/>
-  </r>
-  <r>
-    <x v="18"/>
-  </r>
-  <r>
-    <x v="34"/>
-  </r>
-  <r>
-    <x v="34"/>
-  </r>
-  <r>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="7"/>
-  </r>
-  <r>
-    <x v="6"/>
-  </r>
-  <r>
-    <x v="14"/>
-  </r>
-  <r>
-    <x v="12"/>
-  </r>
-  <r>
-    <x v="7"/>
-  </r>
-  <r>
-    <x v="3"/>
-  </r>
-  <r>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="16"/>
-  </r>
-  <r>
-    <x v="19"/>
-  </r>
-  <r>
-    <x v="27"/>
-  </r>
-  <r>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="4"/>
-  </r>
-  <r>
-    <x v="4"/>
-  </r>
-  <r>
-    <x v="7"/>
-  </r>
-  <r>
-    <x v="24"/>
-  </r>
-  <r>
-    <x v="35"/>
-  </r>
-  <r>
-    <x v="7"/>
-  </r>
-  <r>
-    <x v="11"/>
-  </r>
-  <r>
-    <x v="3"/>
-  </r>
-  <r>
-    <x v="30"/>
-  </r>
-  <r>
-    <x v="7"/>
-  </r>
-  <r>
-    <x v="3"/>
-  </r>
-  <r>
-    <x v="30"/>
-  </r>
-  <r>
-    <x v="4"/>
-  </r>
-  <r>
-    <x v="4"/>
-  </r>
-  <r>
-    <x v="30"/>
-  </r>
-  <r>
-    <x v="36"/>
-  </r>
-  <r>
-    <x v="18"/>
-  </r>
-  <r>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="30"/>
-  </r>
-  <r>
     <x v="15"/>
   </r>
   <r>
-    <x v="32"/>
-  </r>
-  <r>
-    <x v="15"/>
-  </r>
-  <r>
-    <x v="4"/>
-  </r>
-  <r>
-    <x v="4"/>
-  </r>
-  <r>
-    <x v="37"/>
-  </r>
-  <r>
-    <x v="27"/>
-  </r>
-  <r>
-    <x v="38"/>
-  </r>
-  <r>
-    <x v="16"/>
-  </r>
-  <r>
-    <x v="29"/>
-  </r>
-  <r>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="30"/>
-  </r>
-  <r>
-    <x v="30"/>
-  </r>
-  <r>
-    <x v="16"/>
-  </r>
-  <r>
-    <x v="39"/>
-  </r>
-  <r>
     <x v="26"/>
-  </r>
-  <r>
-    <x v="31"/>
-  </r>
-  <r>
-    <x v="10"/>
-  </r>
-  <r>
-    <x v="40"/>
-  </r>
-  <r>
-    <x v="27"/>
-  </r>
-  <r>
-    <x v="41"/>
-  </r>
-  <r>
-    <x v="26"/>
-  </r>
-  <r>
-    <x v="31"/>
-  </r>
-  <r>
-    <x v="32"/>
-  </r>
-  <r>
-    <x v="29"/>
-  </r>
-  <r>
-    <x v="4"/>
-  </r>
-  <r>
-    <x v="4"/>
-  </r>
-  <r>
-    <x v="27"/>
-  </r>
-  <r>
-    <x v="30"/>
-  </r>
-  <r>
-    <x v="16"/>
-  </r>
-  <r>
-    <x v="27"/>
-  </r>
-  <r>
-    <x v="27"/>
-  </r>
-  <r>
-    <x v="42"/>
-  </r>
-  <r>
-    <x v="27"/>
-  </r>
-  <r>
-    <x v="10"/>
-  </r>
-  <r>
-    <x v="29"/>
-  </r>
-  <r>
-    <x v="27"/>
-  </r>
-  <r>
-    <x v="4"/>
-  </r>
-  <r>
-    <x v="4"/>
-  </r>
-  <r>
-    <x v="10"/>
-  </r>
-  <r>
-    <x v="17"/>
-  </r>
-  <r>
-    <x v="43"/>
-  </r>
-  <r>
-    <x v="27"/>
-  </r>
-  <r>
-    <x v="29"/>
-  </r>
-  <r>
-    <x v="35"/>
-  </r>
-  <r>
-    <x v="27"/>
-  </r>
-  <r>
-    <x v="16"/>
-  </r>
-  <r>
-    <x v="4"/>
-  </r>
-  <r>
-    <x v="4"/>
-  </r>
-  <r>
-    <x v="16"/>
-  </r>
-  <r>
-    <x v="10"/>
-  </r>
-  <r>
-    <x v="44"/>
-  </r>
-  <r>
-    <x v="27"/>
-  </r>
-  <r>
-    <x v="27"/>
-  </r>
-  <r>
-    <x v="37"/>
-  </r>
-  <r>
-    <x v="26"/>
-  </r>
-  <r>
-    <x v="10"/>
-  </r>
-  <r>
-    <x v="14"/>
-  </r>
-  <r>
-    <x v="45"/>
-  </r>
-  <r>
-    <x v="30"/>
-  </r>
-  <r>
-    <x v="34"/>
-  </r>
-  <r>
-    <x v="18"/>
-  </r>
-  <r>
-    <x v="46"/>
-  </r>
-  <r>
-    <x v="29"/>
-  </r>
-  <r>
-    <x v="29"/>
-  </r>
-  <r>
-    <x v="30"/>
-  </r>
-  <r>
-    <x v="29"/>
-  </r>
-  <r>
-    <x v="16"/>
-  </r>
-  <r>
-    <x v="16"/>
-  </r>
-  <r>
-    <x v="4"/>
-  </r>
-  <r>
-    <x v="4"/>
-  </r>
-  <r>
-    <x v="47"/>
-  </r>
-  <r>
-    <x v="16"/>
-  </r>
-  <r>
-    <x v="30"/>
-  </r>
-  <r>
-    <x v="25"/>
-  </r>
-  <r>
-    <x v="16"/>
-  </r>
-  <r>
-    <x v="32"/>
-  </r>
-  <r>
-    <x v="16"/>
-  </r>
-  <r>
-    <x v="27"/>
-  </r>
-  <r>
-    <x v="27"/>
-  </r>
-  <r>
-    <x v="16"/>
-  </r>
-  <r>
-    <x v="4"/>
-  </r>
-  <r>
-    <x v="4"/>
-  </r>
-  <r>
-    <x v="29"/>
-  </r>
-  <r>
-    <x v="29"/>
-  </r>
-  <r>
-    <x v="16"/>
-  </r>
-  <r>
-    <x v="16"/>
-  </r>
-  <r>
-    <x v="27"/>
-  </r>
-  <r>
-    <x v="10"/>
-  </r>
-  <r>
-    <x v="16"/>
-  </r>
-  <r>
-    <x v="10"/>
-  </r>
-  <r>
-    <x v="4"/>
-  </r>
-  <r>
-    <x v="4"/>
-  </r>
-  <r>
-    <x v="27"/>
-  </r>
-  <r>
-    <x v="8"/>
-  </r>
-  <r>
-    <x v="46"/>
-  </r>
-  <r>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="30"/>
-  </r>
-  <r>
-    <x v="27"/>
-  </r>
-  <r>
-    <x v="48"/>
-  </r>
-  <r>
-    <x v="27"/>
-  </r>
-  <r>
-    <x v="29"/>
-  </r>
-  <r>
-    <x v="25"/>
-  </r>
-  <r>
-    <x v="27"/>
-  </r>
-  <r>
-    <x v="10"/>
-  </r>
-  <r>
-    <x v="49"/>
-  </r>
-  <r>
-    <x v="15"/>
-  </r>
-  <r>
-    <x v="14"/>
-  </r>
-  <r>
-    <x v="37"/>
-  </r>
-  <r>
-    <x v="27"/>
-  </r>
-  <r>
-    <x v="48"/>
-  </r>
-  <r>
-    <x v="37"/>
-  </r>
-  <r>
-    <x v="27"/>
-  </r>
-  <r>
-    <x v="4"/>
-  </r>
-  <r>
-    <x v="4"/>
-  </r>
-  <r>
-    <x v="16"/>
-  </r>
-  <r>
-    <x v="37"/>
-  </r>
-  <r>
-    <x v="25"/>
-  </r>
-  <r>
-    <x v="10"/>
-  </r>
-  <r>
-    <x v="46"/>
-  </r>
-  <r>
-    <x v="43"/>
-  </r>
-  <r>
-    <x v="14"/>
-  </r>
-  <r>
-    <x v="16"/>
-  </r>
-  <r>
-    <x v="16"/>
-  </r>
-  <r>
-    <x v="24"/>
-  </r>
-  <r>
-    <x v="4"/>
-  </r>
-  <r>
-    <x v="4"/>
-  </r>
-  <r>
-    <x v="27"/>
-  </r>
-  <r>
-    <x v="10"/>
-  </r>
-  <r>
-    <x v="8"/>
-  </r>
-  <r>
-    <x v="35"/>
-  </r>
-  <r>
-    <x v="13"/>
-  </r>
-  <r>
-    <x v="30"/>
-  </r>
-  <r>
-    <x v="37"/>
-  </r>
-  <r>
-    <x v="35"/>
-  </r>
-  <r>
-    <x v="4"/>
-  </r>
-  <r>
-    <x v="4"/>
-  </r>
-  <r>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="29"/>
-  </r>
-  <r>
-    <x v="50"/>
-  </r>
-  <r>
-    <x v="29"/>
-  </r>
-  <r>
-    <x v="16"/>
-  </r>
-  <r>
-    <x v="29"/>
-  </r>
-  <r>
-    <x v="27"/>
-  </r>
-  <r>
-    <x v="35"/>
-  </r>
-  <r>
-    <x v="27"/>
-  </r>
-  <r>
-    <x v="27"/>
-  </r>
-  <r>
-    <x v="24"/>
-  </r>
-  <r>
-    <x v="44"/>
-  </r>
-  <r>
-    <x v="32"/>
-  </r>
-  <r>
-    <x v="10"/>
-  </r>
-  <r>
-    <x v="16"/>
-  </r>
-  <r>
-    <x v="27"/>
   </r>
   <r>
     <x v="51"/>
@@ -1569,7 +1566,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{63FAC1E4-48DE-47B8-8A9B-F039882C55D7}" name="TablaDinámica2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{63FAC1E4-48DE-47B8-8A9B-F039882C55D7}" name="TablaDinámica2" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:B56" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="1">
     <pivotField axis="axisRow" dataField="1" showAll="0">
@@ -1578,54 +1575,54 @@
         <item x="0"/>
         <item x="6"/>
         <item x="1"/>
-        <item x="25"/>
+        <item x="24"/>
         <item x="41"/>
-        <item x="27"/>
-        <item x="20"/>
+        <item x="26"/>
+        <item x="19"/>
         <item x="38"/>
         <item x="3"/>
         <item x="48"/>
         <item x="35"/>
         <item x="42"/>
-        <item x="34"/>
-        <item x="18"/>
-        <item x="14"/>
         <item x="33"/>
-        <item x="29"/>
+        <item x="17"/>
+        <item x="13"/>
+        <item x="32"/>
+        <item x="28"/>
         <item x="49"/>
         <item x="9"/>
-        <item x="12"/>
-        <item x="15"/>
+        <item x="14"/>
         <item x="43"/>
         <item x="40"/>
         <item x="10"/>
         <item x="2"/>
-        <item x="16"/>
-        <item x="24"/>
+        <item x="15"/>
+        <item x="34"/>
         <item x="46"/>
         <item x="50"/>
-        <item x="17"/>
-        <item x="23"/>
+        <item x="16"/>
+        <item x="22"/>
         <item x="7"/>
         <item x="39"/>
-        <item x="31"/>
+        <item x="30"/>
         <item x="47"/>
-        <item x="28"/>
-        <item x="26"/>
+        <item x="27"/>
+        <item x="25"/>
         <item x="44"/>
-        <item x="30"/>
+        <item x="29"/>
         <item x="45"/>
         <item x="37"/>
         <item x="11"/>
-        <item x="32"/>
-        <item x="22"/>
-        <item x="19"/>
+        <item x="31"/>
         <item x="21"/>
+        <item x="18"/>
+        <item x="20"/>
         <item x="8"/>
         <item x="5"/>
-        <item x="13"/>
+        <item x="12"/>
         <item x="51"/>
         <item x="4"/>
+        <item x="23"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -2137,7 +2134,7 @@
         <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>8</v>
@@ -2190,19 +2187,19 @@
         <v>20</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L2" s="2" t="s">
         <v>22</v>
       </c>
       <c r="M2" s="5" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="N2" s="2" t="s">
         <v>23</v>
       </c>
       <c r="O2" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
@@ -2237,19 +2234,19 @@
         <v>25</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="L3" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="M3" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="N3" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="M3" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="N3" s="2" t="s">
+      <c r="O3" s="2" t="s">
         <v>28</v>
-      </c>
-      <c r="O3" s="2" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
@@ -2257,10 +2254,10 @@
         <v>14</v>
       </c>
       <c r="B4" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4" s="5" t="s">
         <v>30</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>31</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>18</v>
@@ -2269,7 +2266,7 @@
         <v>17</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G4" s="5" t="s">
         <v>18</v>
@@ -2281,22 +2278,22 @@
         <v>2</v>
       </c>
       <c r="J4" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="K4" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="K4" s="5" t="s">
+      <c r="L4" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="M4" s="5" t="s">
         <v>34</v>
-      </c>
-      <c r="L4" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="M4" s="5" t="s">
-        <v>35</v>
       </c>
       <c r="N4" s="5" t="s">
         <v>22</v>
       </c>
       <c r="O4" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
@@ -2304,10 +2301,10 @@
         <v>14</v>
       </c>
       <c r="B5" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" s="5" t="s">
         <v>30</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>31</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>18</v>
@@ -2316,7 +2313,7 @@
         <v>17</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G5" s="5" t="s">
         <v>17</v>
@@ -2328,45 +2325,45 @@
         <v>2</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="L5" s="5" t="s">
         <v>20</v>
       </c>
       <c r="M5" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="N5" s="5" t="s">
         <v>22</v>
       </c>
       <c r="O5" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="E6" s="2" t="s">
-        <v>42</v>
-      </c>
       <c r="F6" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H6" s="3">
         <v>2</v>
@@ -2383,25 +2380,25 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="C7" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="E7" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>42</v>
-      </c>
       <c r="F7" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H7" s="4">
         <v>0</v>
@@ -2418,46 +2415,46 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B8" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C8" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="D8" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="E8" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="F8" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="G8" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="H8" s="3">
+        <v>2</v>
+      </c>
+      <c r="I8" s="3">
+        <v>2</v>
+      </c>
+      <c r="J8" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="K8" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="G8" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="H8" s="3">
-        <v>2</v>
-      </c>
-      <c r="I8" s="3">
-        <v>2</v>
-      </c>
-      <c r="J8" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="K8" s="5" t="s">
+      <c r="L8" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="L8" s="5" t="s">
+      <c r="M8" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="N8" s="5" t="s">
         <v>49</v>
-      </c>
-      <c r="M8" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="N8" s="5" t="s">
-        <v>50</v>
       </c>
       <c r="O8" s="5" t="s">
         <v>22</v>
@@ -2465,25 +2462,25 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B9" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C9" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="D9" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="E9" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="E9" s="5" t="s">
-        <v>46</v>
-      </c>
       <c r="F9" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H9" s="4">
         <v>0</v>
@@ -2492,10 +2489,10 @@
         <v>2</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="K9" s="5" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="L9" s="5" t="s">
         <v>21</v>
@@ -2507,45 +2504,45 @@
         <v>22</v>
       </c>
       <c r="O9" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="D10" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="E10" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="F10" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="G10" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H10" s="3">
+        <v>2</v>
+      </c>
+      <c r="I10" s="3">
+        <v>2</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="L10" s="2" t="s">
         <v>57</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="H10" s="3">
-        <v>2</v>
-      </c>
-      <c r="I10" s="3">
-        <v>2</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="L10" s="2" t="s">
-        <v>58</v>
       </c>
       <c r="M10" s="2" t="s">
         <v>22</v>
@@ -2554,30 +2551,30 @@
         <v>23</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B11" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="D11" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="E11" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="E11" s="2" t="s">
-        <v>56</v>
-      </c>
       <c r="F11" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H11" s="4">
         <v>0</v>
@@ -2586,92 +2583,92 @@
         <v>2</v>
       </c>
       <c r="J11" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="K11" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="K11" s="2" t="s">
+      <c r="L11" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="M11" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="N11" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="O11" s="2" t="s">
         <v>61</v>
-      </c>
-      <c r="L11" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="M11" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="N11" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="O11" s="2" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B12" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C12" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="D12" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="F12" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="D12" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="F12" s="5" t="s">
+      <c r="G12" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="H12" s="3">
+        <v>2</v>
+      </c>
+      <c r="I12" s="3">
+        <v>2</v>
+      </c>
+      <c r="J12" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="K12" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L12" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="G12" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="H12" s="3">
-        <v>2</v>
-      </c>
-      <c r="I12" s="3">
-        <v>2</v>
-      </c>
-      <c r="J12" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="K12" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="L12" s="5" t="s">
-        <v>66</v>
-      </c>
       <c r="M12" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="N12" s="5" t="s">
         <v>22</v>
       </c>
       <c r="O12" s="5" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B13" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C13" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="C13" s="5" t="s">
-        <v>64</v>
-      </c>
       <c r="D13" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="E13" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="E13" s="5" t="s">
-        <v>56</v>
-      </c>
       <c r="F13" s="5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H13" s="6">
         <v>1</v>
@@ -2680,42 +2677,42 @@
         <v>2</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="K13" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="M13" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N13" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="L13" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="M13" s="5" t="s">
+      <c r="O13" s="5" t="s">
         <v>68</v>
-      </c>
-      <c r="N13" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="O13" s="5" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B14" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>70</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>71</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E14" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="F14" s="2" t="s">
         <v>72</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>73</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>18</v>
@@ -2727,45 +2724,45 @@
         <v>2</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="L14" s="2" t="s">
         <v>23</v>
       </c>
       <c r="M14" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="N14" s="2" t="s">
         <v>22</v>
       </c>
       <c r="O14" s="5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B15" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>70</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>71</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H15" s="4">
         <v>0</v>
@@ -2774,19 +2771,19 @@
         <v>2</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="K15" s="2" t="s">
         <v>23</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N15" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O15" s="2" t="s">
         <v>22</v>
@@ -2794,46 +2791,46 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B16" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="C16" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="D16" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="D16" s="5" t="s">
+      <c r="E16" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="F16" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="E16" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F16" s="5" t="s">
+      <c r="G16" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="H16" s="3">
+        <v>2</v>
+      </c>
+      <c r="I16" s="3">
+        <v>2</v>
+      </c>
+      <c r="J16" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="G16" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="H16" s="3">
-        <v>2</v>
-      </c>
-      <c r="I16" s="3">
-        <v>2</v>
-      </c>
-      <c r="J16" s="5" t="s">
-        <v>79</v>
-      </c>
       <c r="K16" s="5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="M16" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="N16" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O16" s="5" t="s">
         <v>22</v>
@@ -2841,25 +2838,25 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B17" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="C17" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="D17" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="D17" s="5" t="s">
-        <v>77</v>
-      </c>
       <c r="E17" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H17" s="6">
         <v>1</v>
@@ -2868,45 +2865,45 @@
         <v>2</v>
       </c>
       <c r="J17" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="K17" s="5" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="L17" s="5" t="s">
         <v>23</v>
       </c>
       <c r="M17" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="N17" s="5" t="s">
         <v>22</v>
       </c>
       <c r="O17" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B18" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="C18" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="C18" s="2" t="s">
-        <v>84</v>
-      </c>
       <c r="D18" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H18" s="3">
         <v>2</v>
@@ -2923,22 +2920,22 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B19" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="C19" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="C19" s="2" t="s">
-        <v>84</v>
-      </c>
       <c r="D19" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>18</v>
@@ -2958,26 +2955,26 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B20" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="F20" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="G20" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="D20" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="F20" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="G20" s="5" t="s">
-        <v>55</v>
-      </c>
       <c r="H20" s="3">
         <v>2</v>
       </c>
@@ -2985,7 +2982,7 @@
         <v>2</v>
       </c>
       <c r="J20" s="5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="K20" s="5" t="s">
         <v>20</v>
@@ -2994,36 +2991,36 @@
         <v>23</v>
       </c>
       <c r="M20" s="5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N20" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O20" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C21" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="D21" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="D21" s="5" t="s">
+      <c r="E21" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="E21" s="5" t="s">
-        <v>56</v>
-      </c>
       <c r="F21" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H21" s="4">
         <v>0</v>
@@ -3032,42 +3029,42 @@
         <v>2</v>
       </c>
       <c r="J21" s="5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="K21" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="L21" s="5" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="M21" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="N21" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O21" s="5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B22" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>90</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>91</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>18</v>
@@ -3079,45 +3076,45 @@
         <v>2</v>
       </c>
       <c r="J22" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="K22" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="L22" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="K22" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="L22" s="2" t="s">
-        <v>34</v>
-      </c>
       <c r="M22" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="N22" s="2" t="s">
         <v>22</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B23" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>90</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>91</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H23" s="6">
         <v>1</v>
@@ -3126,45 +3123,45 @@
         <v>2</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="L23" s="2" t="s">
         <v>20</v>
       </c>
       <c r="M23" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="N23" s="2" t="s">
         <v>22</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B24" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="C24" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="C24" s="5" t="s">
+      <c r="D24" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="D24" s="5" t="s">
+      <c r="E24" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="E24" s="5" t="s">
+      <c r="F24" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="F24" s="5" t="s">
-        <v>98</v>
-      </c>
       <c r="G24" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H24" s="3">
         <v>2</v>
@@ -3173,7 +3170,7 @@
         <v>2</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="K24" s="5" t="s">
         <v>22</v>
@@ -3182,36 +3179,36 @@
         <v>23</v>
       </c>
       <c r="M24" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="N24" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O24" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B25" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="C25" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="C25" s="5" t="s">
+      <c r="D25" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="D25" s="5" t="s">
+      <c r="E25" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="E25" s="5" t="s">
-        <v>97</v>
-      </c>
       <c r="F25" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H25" s="4">
         <v>0</v>
@@ -3223,16 +3220,16 @@
         <v>22</v>
       </c>
       <c r="K25" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="L25" s="5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="M25" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N25" s="5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="O25" s="5" t="s">
         <v>23</v>
@@ -3240,25 +3237,25 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B26" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C26" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="D26" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F26" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="D26" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>102</v>
-      </c>
       <c r="G26" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H26" s="3">
         <v>2</v>
@@ -3267,45 +3264,45 @@
         <v>2</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="K26" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="L26" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="L26" s="2" t="s">
-        <v>35</v>
-      </c>
       <c r="M26" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="N26" s="2" t="s">
         <v>22</v>
       </c>
       <c r="O26" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B27" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C27" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="C27" s="2" t="s">
-        <v>101</v>
-      </c>
       <c r="D27" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H27" s="4">
         <v>0</v>
@@ -3314,45 +3311,45 @@
         <v>2</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="K27" s="2" t="s">
         <v>23</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="M27" s="2" t="s">
         <v>22</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="O27" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B28" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="C28" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="C28" s="5" t="s">
+      <c r="D28" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="F28" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="D28" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="E28" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="F28" s="5" t="s">
-        <v>106</v>
-      </c>
       <c r="G28" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H28" s="3">
         <v>2</v>
@@ -3369,25 +3366,25 @@
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B29" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="C29" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="C29" s="5" t="s">
-        <v>105</v>
-      </c>
       <c r="D29" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="E29" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="E29" s="5" t="s">
-        <v>97</v>
-      </c>
       <c r="F29" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H29" s="4">
         <v>0</v>
@@ -3404,25 +3401,25 @@
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B30" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C30" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="D30" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="D30" s="2" t="s">
-        <v>77</v>
-      </c>
       <c r="E30" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H30" s="3">
         <v>2</v>
@@ -3431,45 +3428,45 @@
         <v>2</v>
       </c>
       <c r="J30" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="K30" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="K30" s="2" t="s">
+      <c r="L30" s="2" t="s">
         <v>35</v>
-      </c>
-      <c r="L30" s="2" t="s">
-        <v>36</v>
       </c>
       <c r="M30" s="2" t="s">
         <v>22</v>
       </c>
       <c r="N30" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O30" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B31" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C31" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="D31" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="D31" s="2" t="s">
-        <v>77</v>
-      </c>
       <c r="E31" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H31" s="6">
         <v>1</v>
@@ -3478,92 +3475,92 @@
         <v>2</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="K31" s="2" t="s">
         <v>23</v>
       </c>
       <c r="L31" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="O31" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="B32" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="B32" s="5" t="s">
+      <c r="C32" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="C32" s="5" t="s">
+      <c r="D32" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="E32" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="F32" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="D32" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="E32" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="F32" s="5" t="s">
+      <c r="G32" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="H32" s="3">
+        <v>2</v>
+      </c>
+      <c r="I32" s="3">
+        <v>2</v>
+      </c>
+      <c r="J32" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="G32" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="H32" s="3">
-        <v>2</v>
-      </c>
-      <c r="I32" s="3">
-        <v>2</v>
-      </c>
-      <c r="J32" s="5" t="s">
+      <c r="K32" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="L32" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="M32" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="K32" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="L32" s="5" t="s">
-        <v>163</v>
-      </c>
-      <c r="M32" s="5" t="s">
-        <v>115</v>
-      </c>
       <c r="N32" s="5" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="O32" s="5" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="B33" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="B33" s="5" t="s">
+      <c r="C33" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="C33" s="5" t="s">
-        <v>112</v>
-      </c>
       <c r="D33" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="E33" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="E33" s="5" t="s">
-        <v>97</v>
-      </c>
       <c r="F33" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H33" s="6">
         <v>1</v>
@@ -3572,45 +3569,45 @@
         <v>2</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="K33" s="5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="L33" s="5" t="s">
         <v>22</v>
       </c>
       <c r="M33" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="N33" s="5" t="s">
         <v>20</v>
       </c>
       <c r="O33" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B34" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C34" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="D34" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="D34" s="2" t="s">
+      <c r="E34" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="E34" s="2" t="s">
+      <c r="F34" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="F34" s="2" t="s">
-        <v>122</v>
-      </c>
       <c r="G34" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H34" s="3">
         <v>2</v>
@@ -3622,13 +3619,13 @@
         <v>20</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="M34" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="N34" s="2" t="s">
         <v>23</v>
@@ -3639,25 +3636,25 @@
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B35" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C35" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="C35" s="2" t="s">
+      <c r="D35" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="D35" s="2" t="s">
+      <c r="E35" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="E35" s="2" t="s">
-        <v>121</v>
-      </c>
       <c r="F35" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H35" s="4">
         <v>0</v>
@@ -3666,92 +3663,92 @@
         <v>2</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L35" s="2" t="s">
         <v>20</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="N35" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O35" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B36" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="D36" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="E36" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="F36" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="C36" s="5" t="s">
+      <c r="G36" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="D36" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="E36" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="F36" s="5" t="s">
+      <c r="H36" s="3">
+        <v>2</v>
+      </c>
+      <c r="I36" s="3">
+        <v>2</v>
+      </c>
+      <c r="J36" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="K36" s="5" t="s">
         <v>125</v>
-      </c>
-      <c r="G36" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="H36" s="3">
-        <v>2</v>
-      </c>
-      <c r="I36" s="3">
-        <v>2</v>
-      </c>
-      <c r="J36" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="K36" s="5" t="s">
-        <v>126</v>
       </c>
       <c r="L36" s="5" t="s">
         <v>23</v>
       </c>
       <c r="M36" s="5" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="N36" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O36" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C37" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="D37" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="D37" s="5" t="s">
+      <c r="E37" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="E37" s="5" t="s">
-        <v>97</v>
-      </c>
       <c r="F37" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G37" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H37" s="4">
         <v>0</v>
@@ -3760,45 +3757,45 @@
         <v>2</v>
       </c>
       <c r="J37" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="K37" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="L37" s="5" t="s">
         <v>23</v>
       </c>
       <c r="M37" s="5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N37" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O37" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C38" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D38" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="D38" s="2" t="s">
+      <c r="E38" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="E38" s="2" t="s">
-        <v>97</v>
-      </c>
       <c r="F38" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H38" s="3">
         <v>2</v>
@@ -3807,7 +3804,7 @@
         <v>2</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="K38" s="2" t="s">
         <v>20</v>
@@ -3816,36 +3813,36 @@
         <v>22</v>
       </c>
       <c r="M38" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O38" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C39" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D39" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="D39" s="2" t="s">
+      <c r="E39" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="E39" s="2" t="s">
-        <v>97</v>
-      </c>
       <c r="F39" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H39" s="4">
         <v>0</v>
@@ -3854,45 +3851,45 @@
         <v>2</v>
       </c>
       <c r="J39" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="K39" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="L39" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="K39" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="L39" s="2" t="s">
+      <c r="M39" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="M39" s="2" t="s">
-        <v>131</v>
-      </c>
       <c r="N39" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="O39" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B40" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="C40" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="C40" s="5" t="s">
+      <c r="D40" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="D40" s="5" t="s">
+      <c r="E40" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="F40" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="E40" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="F40" s="5" t="s">
-        <v>135</v>
-      </c>
       <c r="G40" s="5" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H40" s="3">
         <v>2</v>
@@ -3904,16 +3901,16 @@
         <v>22</v>
       </c>
       <c r="K40" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="L40" s="5" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="M40" s="5" t="s">
         <v>23</v>
       </c>
       <c r="N40" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O40" s="5" t="s">
         <v>21</v>
@@ -3921,25 +3918,25 @@
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B41" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="C41" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="C41" s="5" t="s">
+      <c r="D41" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="D41" s="5" t="s">
-        <v>134</v>
-      </c>
       <c r="E41" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G41" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H41" s="6">
         <v>1</v>
@@ -3948,42 +3945,42 @@
         <v>2</v>
       </c>
       <c r="J41" s="5" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="K41" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="L41" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="M41" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="N41" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="O41" s="5" t="s">
         <v>114</v>
-      </c>
-      <c r="L41" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="M41" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="N41" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="O41" s="5" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B42" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C42" s="2" t="s">
         <v>90</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>91</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>18</v>
@@ -3995,45 +3992,45 @@
         <v>2</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="K42" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M42" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N42" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="O42" s="2" t="s">
         <v>34</v>
-      </c>
-      <c r="N42" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="O42" s="2" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B43" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C43" s="2" t="s">
         <v>90</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>91</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H43" s="6">
         <v>1</v>
@@ -4042,45 +4039,45 @@
         <v>2</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="L43" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="M43" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="N43" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="O43" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="B44" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="B44" s="5" t="s">
+      <c r="C44" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="D44" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="E44" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="F44" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="C44" s="5" t="s">
+      <c r="G44" s="5" t="s">
         <v>95</v>
-      </c>
-      <c r="D44" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="E44" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="F44" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="G44" s="5" t="s">
-        <v>96</v>
       </c>
       <c r="H44" s="3">
         <v>2</v>
@@ -4092,16 +4089,16 @@
         <v>20</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="L44" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="M44" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="N44" s="5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="O44" s="5" t="s">
         <v>22</v>
@@ -4109,25 +4106,25 @@
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="B45" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="B45" s="5" t="s">
-        <v>142</v>
-      </c>
       <c r="C45" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="D45" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="D45" s="5" t="s">
+      <c r="E45" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="E45" s="5" t="s">
-        <v>97</v>
-      </c>
       <c r="F45" s="5" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G45" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H45" s="4">
         <v>0</v>
@@ -4136,22 +4133,22 @@
         <v>2</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="K45" s="5" t="s">
         <v>20</v>
       </c>
       <c r="L45" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="M45" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="N45" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="O45" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
   </sheetData>
@@ -4170,15 +4167,15 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="B1" s="7" t="s">
         <v>146</v>
-      </c>
-      <c r="B1" s="7" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B2">
         <v>27</v>
@@ -4194,7 +4191,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B4">
         <v>15</v>
@@ -4210,7 +4207,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B6">
         <v>13</v>
@@ -4218,7 +4215,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B7">
         <v>11</v>
@@ -4234,7 +4231,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B9">
         <v>9</v>
@@ -4242,7 +4239,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B10">
         <v>7</v>
@@ -4250,7 +4247,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B11">
         <v>6</v>
@@ -4258,7 +4255,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B12">
         <v>6</v>
@@ -4266,7 +4263,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B13">
         <v>6</v>
@@ -4274,7 +4271,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B14">
         <v>5</v>
@@ -4282,7 +4279,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B15">
         <v>5</v>
@@ -4290,7 +4287,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B16">
         <v>4</v>
@@ -4298,7 +4295,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="B17">
         <v>4</v>
@@ -4306,7 +4303,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>33</v>
+        <v>168</v>
       </c>
       <c r="B18">
         <v>4</v>
@@ -4314,7 +4311,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="B19">
         <v>4</v>
@@ -4322,7 +4319,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B20">
         <v>3</v>
@@ -4330,7 +4327,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B21">
         <v>3</v>
@@ -4338,7 +4335,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>155</v>
+        <v>21</v>
       </c>
       <c r="B22">
         <v>3</v>
@@ -4346,7 +4343,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B23">
         <v>3</v>
@@ -4354,7 +4351,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B24">
         <v>3</v>
@@ -4362,7 +4359,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B25">
         <v>3</v>
@@ -4370,7 +4367,7 @@
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B26">
         <v>3</v>
@@ -4378,7 +4375,7 @@
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B27">
         <v>3</v>
@@ -4386,7 +4383,7 @@
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B28">
         <v>2</v>
@@ -4394,7 +4391,7 @@
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B29">
         <v>2</v>
@@ -4402,7 +4399,7 @@
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B30">
         <v>2</v>
@@ -4410,7 +4407,7 @@
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B31">
         <v>2</v>
@@ -4418,7 +4415,7 @@
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B32">
         <v>2</v>
@@ -4426,7 +4423,7 @@
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B33">
         <v>2</v>
@@ -4434,7 +4431,7 @@
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B34">
         <v>1</v>
@@ -4450,7 +4447,7 @@
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B36">
         <v>1</v>
@@ -4458,7 +4455,7 @@
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B37">
         <v>1</v>
@@ -4466,7 +4463,7 @@
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B38">
         <v>1</v>
@@ -4474,7 +4471,7 @@
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B39">
         <v>1</v>
@@ -4482,7 +4479,7 @@
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B40">
         <v>1</v>
@@ -4490,7 +4487,7 @@
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B41">
         <v>1</v>
@@ -4498,7 +4495,7 @@
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>26</v>
+        <v>139</v>
       </c>
       <c r="B42">
         <v>1</v>
@@ -4506,7 +4503,7 @@
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="B43">
         <v>1</v>
@@ -4522,7 +4519,7 @@
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>158</v>
+        <v>129</v>
       </c>
       <c r="B45">
         <v>1</v>
@@ -4530,7 +4527,7 @@
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>130</v>
+        <v>49</v>
       </c>
       <c r="B46">
         <v>1</v>
@@ -4538,7 +4535,7 @@
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="B47">
         <v>1</v>
@@ -4546,7 +4543,7 @@
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>61</v>
+        <v>130</v>
       </c>
       <c r="B48">
         <v>1</v>
@@ -4554,7 +4551,7 @@
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="B49">
         <v>1</v>
@@ -4562,17 +4559,9 @@
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>138</v>
+        <v>151</v>
       </c>
       <c r="B50">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>152</v>
-      </c>
-      <c r="B51">
         <v>1</v>
       </c>
     </row>
@@ -4622,8 +4611,8 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:B64" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B64">
-    <sortCondition descending="1" ref="B2:B64"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B50">
+    <sortCondition descending="1" ref="B2:B50"/>
   </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4640,15 +4629,15 @@
   <sheetData>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B4" s="11">
         <v>1</v>
@@ -4664,7 +4653,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B6" s="11">
         <v>3</v>
@@ -4680,7 +4669,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B8" s="11">
         <v>4</v>
@@ -4688,7 +4677,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B9" s="11">
         <v>1</v>
@@ -4696,7 +4685,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B10" s="11">
         <v>27</v>
@@ -4704,7 +4693,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B11" s="11">
         <v>1</v>
@@ -4712,7 +4701,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B12" s="11">
         <v>1</v>
@@ -4720,7 +4709,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B13" s="11">
         <v>11</v>
@@ -4728,7 +4717,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B14" s="11">
         <v>2</v>
@@ -4736,7 +4725,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="10" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B15" s="11">
         <v>5</v>
@@ -4744,7 +4733,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B16" s="11">
         <v>1</v>
@@ -4752,7 +4741,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B17" s="11">
         <v>3</v>
@@ -4760,7 +4749,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B18" s="11">
         <v>7</v>
@@ -4768,7 +4757,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B19" s="11">
         <v>9</v>
@@ -4776,7 +4765,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B20" s="11">
         <v>1</v>
@@ -4784,7 +4773,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B21" s="11">
         <v>15</v>
@@ -4792,7 +4781,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="10" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B22" s="11">
         <v>1</v>
@@ -4800,135 +4789,135 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="10" t="s">
-        <v>26</v>
+        <v>154</v>
       </c>
       <c r="B23" s="11">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="10" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="B24" s="11">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="10" t="s">
-        <v>169</v>
+        <v>68</v>
       </c>
       <c r="B25" s="11">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="10" t="s">
-        <v>69</v>
+        <v>139</v>
       </c>
       <c r="B26" s="11">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="10" t="s">
-        <v>140</v>
+        <v>61</v>
       </c>
       <c r="B27" s="11">
-        <v>1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="10" t="s">
-        <v>62</v>
+        <v>32</v>
       </c>
       <c r="B28" s="11">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="10" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="B29" s="11">
-        <v>4</v>
+        <v>23</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B30" s="11">
-        <v>23</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="10" t="s">
-        <v>21</v>
+        <v>159</v>
       </c>
       <c r="B31" s="11">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="10" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="B32" s="11">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="10" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="B33" s="11">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="10" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="B34" s="11">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" s="10" t="s">
-        <v>158</v>
+        <v>48</v>
       </c>
       <c r="B35" s="11">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" s="10" t="s">
-        <v>49</v>
+        <v>129</v>
       </c>
       <c r="B36" s="11">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" s="10" t="s">
-        <v>130</v>
+        <v>153</v>
       </c>
       <c r="B37" s="11">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" s="10" t="s">
-        <v>154</v>
+        <v>49</v>
       </c>
       <c r="B38" s="11">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" s="10" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="B39" s="11">
         <v>1</v>
@@ -4936,103 +4925,103 @@
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" s="10" t="s">
-        <v>61</v>
+        <v>152</v>
       </c>
       <c r="B40" s="11">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" s="10" t="s">
-        <v>153</v>
+        <v>114</v>
       </c>
       <c r="B41" s="11">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" s="10" t="s">
-        <v>115</v>
+        <v>23</v>
       </c>
       <c r="B42" s="11">
-        <v>2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" s="10" t="s">
-        <v>23</v>
+        <v>130</v>
       </c>
       <c r="B43" s="11">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" s="10" t="s">
-        <v>131</v>
+        <v>35</v>
       </c>
       <c r="B44" s="11">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" s="10" t="s">
-        <v>36</v>
+        <v>65</v>
       </c>
       <c r="B45" s="11">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" s="10" t="s">
-        <v>66</v>
+        <v>34</v>
       </c>
       <c r="B46" s="11">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" s="10" t="s">
-        <v>35</v>
+        <v>137</v>
       </c>
       <c r="B47" s="11">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" s="10" t="s">
-        <v>138</v>
+        <v>26</v>
       </c>
       <c r="B48" s="11">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" s="10" t="s">
-        <v>27</v>
+        <v>151</v>
       </c>
       <c r="B49" s="11">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" s="10" t="s">
-        <v>152</v>
+        <v>59</v>
       </c>
       <c r="B50" s="11">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" s="10" t="s">
-        <v>60</v>
+        <v>155</v>
       </c>
       <c r="B51" s="11">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" s="10" t="s">
-        <v>156</v>
+        <v>78</v>
       </c>
       <c r="B52" s="11">
         <v>2</v>
@@ -5040,29 +5029,29 @@
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="B53" s="11">
-        <v>2</v>
-      </c>
+        <v>165</v>
+      </c>
+      <c r="B53" s="11"/>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A54" s="10" t="s">
-        <v>166</v>
-      </c>
-      <c r="B54" s="11"/>
+      <c r="A54" s="10">
+        <v>0</v>
+      </c>
+      <c r="B54" s="11">
+        <v>36</v>
+      </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A55" s="10">
-        <v>0</v>
+      <c r="A55" s="10" t="s">
+        <v>169</v>
       </c>
       <c r="B55" s="11">
-        <v>36</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" s="10" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B56" s="11">
         <v>264</v>
@@ -5107,7 +5096,7 @@
   <sheetData>
     <row r="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="2" spans="2:2" x14ac:dyDescent="0.25">
@@ -5377,7 +5366,7 @@
     <row r="46" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B46" s="2" t="str">
         <f>Resultados!K2</f>
-        <v>Kommo_o</v>
+        <v>kommo</v>
       </c>
     </row>
     <row r="47" spans="2:2" x14ac:dyDescent="0.25">

--- a/resultados_torneo.xlsx
+++ b/resultados_torneo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Downloads\preubas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78F2EF32-4CD4-4CDE-AE02-C2D1AC7E5322}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82138C3B-D49B-476A-9618-31FA562658B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Resultados" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="3" r:id="rId5"/>
+    <pivotCache cacheId="0" r:id="rId5"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="657" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="657" uniqueCount="169">
   <si>
     <t>Semana/Fecha</t>
   </si>
@@ -280,9 +280,6 @@
   </si>
   <si>
     <t>Juanjo</t>
-  </si>
-  <si>
-    <t>Kommo-O</t>
   </si>
   <si>
     <t>10/05/2026</t>
@@ -1566,7 +1563,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{63FAC1E4-48DE-47B8-8A9B-F039882C55D7}" name="TablaDinámica2" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{63FAC1E4-48DE-47B8-8A9B-F039882C55D7}" name="TablaDinámica2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:B56" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="1">
     <pivotField axis="axisRow" dataField="1" showAll="0">
@@ -2134,7 +2131,7 @@
         <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>8</v>
@@ -2187,19 +2184,19 @@
         <v>20</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="L2" s="2" t="s">
         <v>22</v>
       </c>
       <c r="M2" s="5" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="N2" s="2" t="s">
         <v>23</v>
       </c>
       <c r="O2" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
@@ -2234,13 +2231,13 @@
         <v>25</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="L3" s="2" t="s">
         <v>26</v>
       </c>
       <c r="M3" s="5" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="N3" s="2" t="s">
         <v>27</v>
@@ -2284,7 +2281,7 @@
         <v>33</v>
       </c>
       <c r="L4" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="M4" s="5" t="s">
         <v>34</v>
@@ -2325,10 +2322,10 @@
         <v>2</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="L5" s="5" t="s">
         <v>20</v>
@@ -2340,7 +2337,7 @@
         <v>22</v>
       </c>
       <c r="O5" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
@@ -2442,7 +2439,7 @@
         <v>2</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="K8" s="5" t="s">
         <v>47</v>
@@ -2451,7 +2448,7 @@
         <v>48</v>
       </c>
       <c r="M8" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="N8" s="5" t="s">
         <v>49</v>
@@ -2492,10 +2489,10 @@
         <v>51</v>
       </c>
       <c r="K9" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="L9" s="5" t="s">
-        <v>21</v>
+        <v>151</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>168</v>
       </c>
       <c r="M9" s="5" t="s">
         <v>23</v>
@@ -2539,7 +2536,7 @@
         <v>48</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="L10" s="2" t="s">
         <v>57</v>
@@ -2592,7 +2589,7 @@
         <v>48</v>
       </c>
       <c r="M11" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="N11" s="2" t="s">
         <v>47</v>
@@ -2630,7 +2627,7 @@
         <v>2</v>
       </c>
       <c r="J12" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="K12" s="5" t="s">
         <v>27</v>
@@ -2639,13 +2636,13 @@
         <v>65</v>
       </c>
       <c r="M12" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="N12" s="5" t="s">
         <v>22</v>
       </c>
       <c r="O12" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
@@ -2683,7 +2680,7 @@
         <v>33</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="M13" s="5" t="s">
         <v>67</v>
@@ -2733,13 +2730,13 @@
         <v>23</v>
       </c>
       <c r="M14" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="N14" s="2" t="s">
         <v>22</v>
       </c>
       <c r="O14" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
@@ -2771,7 +2768,7 @@
         <v>2</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="K15" s="2" t="s">
         <v>23</v>
@@ -2783,7 +2780,7 @@
         <v>61</v>
       </c>
       <c r="N15" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="O15" s="2" t="s">
         <v>22</v>
@@ -2821,16 +2818,16 @@
         <v>78</v>
       </c>
       <c r="K16" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="M16" s="5" t="s">
         <v>27</v>
       </c>
       <c r="N16" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="O16" s="5" t="s">
         <v>22</v>
@@ -2868,30 +2865,30 @@
         <v>51</v>
       </c>
       <c r="K17" s="5" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="L17" s="5" t="s">
         <v>23</v>
       </c>
       <c r="M17" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="N17" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="O17" s="5" t="s">
-        <v>80</v>
+      <c r="O17" s="2" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B18" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="C18" s="2" t="s">
         <v>82</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>83</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>71</v>
@@ -2900,7 +2897,7 @@
         <v>18</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>71</v>
@@ -2920,13 +2917,13 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B19" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="C19" s="2" t="s">
         <v>82</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>83</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>71</v>
@@ -2935,7 +2932,7 @@
         <v>18</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>18</v>
@@ -2955,10 +2952,10 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>53</v>
@@ -2970,7 +2967,7 @@
         <v>55</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G20" s="5" t="s">
         <v>54</v>
@@ -2982,7 +2979,7 @@
         <v>2</v>
       </c>
       <c r="J20" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="K20" s="5" t="s">
         <v>20</v>
@@ -2997,15 +2994,15 @@
         <v>27</v>
       </c>
       <c r="O20" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>53</v>
@@ -3017,7 +3014,7 @@
         <v>55</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G21" s="5" t="s">
         <v>55</v>
@@ -3029,16 +3026,16 @@
         <v>2</v>
       </c>
       <c r="J21" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="K21" s="5" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="L21" s="5" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="M21" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="N21" s="5" t="s">
         <v>27</v>
@@ -3049,13 +3046,13 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B22" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>89</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>90</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>18</v>
@@ -3064,7 +3061,7 @@
         <v>71</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>18</v>
@@ -3096,13 +3093,13 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B23" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>89</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>90</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>18</v>
@@ -3111,7 +3108,7 @@
         <v>71</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>71</v>
@@ -3123,16 +3120,16 @@
         <v>2</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L23" s="2" t="s">
         <v>20</v>
       </c>
       <c r="M23" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="N23" s="2" t="s">
         <v>22</v>
@@ -3143,25 +3140,25 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B24" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="C24" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="C24" s="5" t="s">
+      <c r="D24" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="D24" s="5" t="s">
+      <c r="E24" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="E24" s="5" t="s">
+      <c r="F24" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="F24" s="5" t="s">
-        <v>97</v>
-      </c>
       <c r="G24" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H24" s="3">
         <v>2</v>
@@ -3170,7 +3167,7 @@
         <v>2</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="K24" s="5" t="s">
         <v>22</v>
@@ -3182,7 +3179,7 @@
         <v>27</v>
       </c>
       <c r="N24" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="O24" s="5" t="s">
         <v>78</v>
@@ -3190,25 +3187,25 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B25" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="C25" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="C25" s="5" t="s">
+      <c r="D25" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="D25" s="5" t="s">
+      <c r="E25" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="E25" s="5" t="s">
-        <v>96</v>
-      </c>
       <c r="F25" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H25" s="4">
         <v>0</v>
@@ -3220,10 +3217,10 @@
         <v>22</v>
       </c>
       <c r="K25" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="L25" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="M25" s="5" t="s">
         <v>57</v>
@@ -3237,13 +3234,13 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B26" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C26" s="2" t="s">
         <v>99</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>100</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>76</v>
@@ -3252,7 +3249,7 @@
         <v>44</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>76</v>
@@ -3264,7 +3261,7 @@
         <v>2</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="K26" s="2" t="s">
         <v>33</v>
@@ -3273,7 +3270,7 @@
         <v>34</v>
       </c>
       <c r="M26" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="N26" s="2" t="s">
         <v>22</v>
@@ -3284,13 +3281,13 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B27" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C27" s="2" t="s">
         <v>99</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>100</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>76</v>
@@ -3299,7 +3296,7 @@
         <v>44</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>44</v>
@@ -3311,13 +3308,13 @@
         <v>2</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="K27" s="2" t="s">
         <v>23</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="M27" s="2" t="s">
         <v>22</v>
@@ -3331,25 +3328,25 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B28" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="C28" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="C28" s="5" t="s">
+      <c r="D28" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="F28" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="D28" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="E28" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="F28" s="5" t="s">
-        <v>105</v>
-      </c>
       <c r="G28" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H28" s="3">
         <v>2</v>
@@ -3366,25 +3363,25 @@
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B29" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="C29" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="C29" s="5" t="s">
-        <v>104</v>
-      </c>
       <c r="D29" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="E29" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="E29" s="5" t="s">
-        <v>96</v>
-      </c>
       <c r="F29" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H29" s="4">
         <v>0</v>
@@ -3401,7 +3398,7 @@
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>74</v>
@@ -3416,7 +3413,7 @@
         <v>44</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>76</v>
@@ -3440,7 +3437,7 @@
         <v>22</v>
       </c>
       <c r="N30" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="O30" s="2" t="s">
         <v>32</v>
@@ -3448,7 +3445,7 @@
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>74</v>
@@ -3463,7 +3460,7 @@
         <v>44</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>44</v>
@@ -3475,13 +3472,13 @@
         <v>2</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="K31" s="2" t="s">
         <v>23</v>
       </c>
       <c r="L31" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="M31" s="2" t="s">
         <v>61</v>
@@ -3495,72 +3492,72 @@
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="B32" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="B32" s="5" t="s">
+      <c r="C32" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="C32" s="5" t="s">
+      <c r="D32" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="E32" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="F32" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="D32" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="E32" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="F32" s="5" t="s">
+      <c r="G32" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="H32" s="3">
+        <v>2</v>
+      </c>
+      <c r="I32" s="3">
+        <v>2</v>
+      </c>
+      <c r="J32" s="5" t="s">
         <v>112</v>
-      </c>
-      <c r="G32" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="H32" s="3">
-        <v>2</v>
-      </c>
-      <c r="I32" s="3">
-        <v>2</v>
-      </c>
-      <c r="J32" s="5" t="s">
-        <v>113</v>
       </c>
       <c r="K32" s="5" t="s">
         <v>61</v>
       </c>
       <c r="L32" s="5" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="M32" s="5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="N32" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="O32" s="5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="B33" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="B33" s="5" t="s">
+      <c r="C33" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="C33" s="5" t="s">
-        <v>111</v>
-      </c>
       <c r="D33" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="E33" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="E33" s="5" t="s">
-        <v>96</v>
-      </c>
       <c r="F33" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H33" s="6">
         <v>1</v>
@@ -3569,16 +3566,16 @@
         <v>2</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="K33" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="L33" s="5" t="s">
         <v>22</v>
       </c>
       <c r="M33" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="N33" s="5" t="s">
         <v>20</v>
@@ -3589,25 +3586,25 @@
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B34" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C34" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="D34" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="D34" s="2" t="s">
+      <c r="E34" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="E34" s="2" t="s">
+      <c r="F34" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="F34" s="2" t="s">
-        <v>121</v>
-      </c>
       <c r="G34" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H34" s="3">
         <v>2</v>
@@ -3619,13 +3616,13 @@
         <v>20</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="L34" s="2" t="s">
         <v>27</v>
       </c>
       <c r="M34" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="N34" s="2" t="s">
         <v>23</v>
@@ -3636,25 +3633,25 @@
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B35" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C35" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="C35" s="2" t="s">
+      <c r="D35" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="D35" s="2" t="s">
+      <c r="E35" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="E35" s="2" t="s">
-        <v>120</v>
-      </c>
       <c r="F35" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H35" s="4">
         <v>0</v>
@@ -3663,7 +3660,7 @@
         <v>2</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="K35" s="2" t="s">
         <v>33</v>
@@ -3675,7 +3672,7 @@
         <v>35</v>
       </c>
       <c r="N35" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="O35" s="2" t="s">
         <v>27</v>
@@ -3683,25 +3680,25 @@
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B36" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="D36" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="E36" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="F36" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="C36" s="5" t="s">
+      <c r="G36" s="5" t="s">
         <v>94</v>
-      </c>
-      <c r="D36" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="E36" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="F36" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="G36" s="5" t="s">
-        <v>95</v>
       </c>
       <c r="H36" s="3">
         <v>2</v>
@@ -3713,42 +3710,42 @@
         <v>26</v>
       </c>
       <c r="K36" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="L36" s="5" t="s">
         <v>23</v>
       </c>
       <c r="M36" s="5" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="N36" s="5" t="s">
         <v>28</v>
       </c>
       <c r="O36" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C37" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="D37" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="D37" s="5" t="s">
+      <c r="E37" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="E37" s="5" t="s">
-        <v>96</v>
-      </c>
       <c r="F37" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G37" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H37" s="4">
         <v>0</v>
@@ -3760,7 +3757,7 @@
         <v>26</v>
       </c>
       <c r="K37" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="L37" s="5" t="s">
         <v>23</v>
@@ -3769,7 +3766,7 @@
         <v>61</v>
       </c>
       <c r="N37" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="O37" s="5" t="s">
         <v>57</v>
@@ -3777,25 +3774,25 @@
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C38" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D38" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="D38" s="2" t="s">
+      <c r="E38" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="E38" s="2" t="s">
-        <v>96</v>
-      </c>
       <c r="F38" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H38" s="3">
         <v>2</v>
@@ -3804,7 +3801,7 @@
         <v>2</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="K38" s="2" t="s">
         <v>20</v>
@@ -3813,36 +3810,36 @@
         <v>22</v>
       </c>
       <c r="M38" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="N38" s="2" t="s">
         <v>27</v>
       </c>
       <c r="O38" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C39" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D39" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="D39" s="2" t="s">
+      <c r="E39" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="E39" s="2" t="s">
-        <v>96</v>
-      </c>
       <c r="F39" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H39" s="4">
         <v>0</v>
@@ -3851,45 +3848,45 @@
         <v>2</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="K39" s="2" t="s">
         <v>48</v>
       </c>
       <c r="L39" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="M39" s="2" t="s">
         <v>129</v>
-      </c>
-      <c r="M39" s="2" t="s">
-        <v>130</v>
       </c>
       <c r="N39" s="2" t="s">
         <v>47</v>
       </c>
       <c r="O39" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B40" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="C40" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="C40" s="5" t="s">
+      <c r="D40" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="D40" s="5" t="s">
+      <c r="E40" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="F40" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="E40" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="F40" s="5" t="s">
-        <v>134</v>
-      </c>
       <c r="G40" s="5" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H40" s="3">
         <v>2</v>
@@ -3904,39 +3901,39 @@
         <v>51</v>
       </c>
       <c r="L40" s="5" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="M40" s="5" t="s">
         <v>23</v>
       </c>
       <c r="N40" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="O40" s="5" t="s">
-        <v>21</v>
+        <v>115</v>
+      </c>
+      <c r="O40" s="2" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B41" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="C41" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="C41" s="5" t="s">
+      <c r="D41" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="D41" s="5" t="s">
-        <v>133</v>
-      </c>
       <c r="E41" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G41" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H41" s="6">
         <v>1</v>
@@ -3945,33 +3942,33 @@
         <v>2</v>
       </c>
       <c r="J41" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="K41" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="L41" s="5" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="M41" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="N41" s="5" t="s">
         <v>61</v>
       </c>
       <c r="O41" s="5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B42" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C42" s="2" t="s">
         <v>89</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>90</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>18</v>
@@ -3980,7 +3977,7 @@
         <v>71</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>18</v>
@@ -3992,10 +3989,10 @@
         <v>2</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="K42" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="L42" s="2" t="s">
         <v>61</v>
@@ -4004,7 +4001,7 @@
         <v>33</v>
       </c>
       <c r="N42" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="O42" s="2" t="s">
         <v>34</v>
@@ -4012,13 +4009,13 @@
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B43" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C43" s="2" t="s">
         <v>89</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>90</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>18</v>
@@ -4027,7 +4024,7 @@
         <v>71</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>71</v>
@@ -4039,19 +4036,19 @@
         <v>2</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="K43" s="2" t="s">
         <v>48</v>
       </c>
       <c r="L43" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="M43" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="N43" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="O43" s="2" t="s">
         <v>61</v>
@@ -4059,25 +4056,25 @@
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="B44" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="B44" s="5" t="s">
+      <c r="C44" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="D44" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="E44" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="F44" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="C44" s="5" t="s">
+      <c r="G44" s="5" t="s">
         <v>94</v>
-      </c>
-      <c r="D44" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="E44" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="F44" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="G44" s="5" t="s">
-        <v>95</v>
       </c>
       <c r="H44" s="3">
         <v>2</v>
@@ -4089,16 +4086,16 @@
         <v>20</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="L44" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="M44" s="5" t="s">
         <v>27</v>
       </c>
       <c r="N44" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="O44" s="5" t="s">
         <v>22</v>
@@ -4106,25 +4103,25 @@
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="B45" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="B45" s="5" t="s">
-        <v>141</v>
-      </c>
       <c r="C45" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="D45" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="D45" s="5" t="s">
+      <c r="E45" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="E45" s="5" t="s">
-        <v>96</v>
-      </c>
       <c r="F45" s="5" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G45" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H45" s="4">
         <v>0</v>
@@ -4133,13 +4130,13 @@
         <v>2</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="K45" s="5" t="s">
         <v>20</v>
       </c>
       <c r="L45" s="5" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="M45" s="5" t="s">
         <v>27</v>
@@ -4148,7 +4145,7 @@
         <v>35</v>
       </c>
       <c r="O45" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
   </sheetData>
@@ -4167,15 +4164,15 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="B1" s="7" t="s">
         <v>145</v>
-      </c>
-      <c r="B1" s="7" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B2">
         <v>27</v>
@@ -4215,7 +4212,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B7">
         <v>11</v>
@@ -4231,7 +4228,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B9">
         <v>9</v>
@@ -4279,7 +4276,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B15">
         <v>5</v>
@@ -4295,7 +4292,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B17">
         <v>4</v>
@@ -4303,7 +4300,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B18">
         <v>4</v>
@@ -4327,7 +4324,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B21">
         <v>3</v>
@@ -4343,7 +4340,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B23">
         <v>3</v>
@@ -4351,7 +4348,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B24">
         <v>3</v>
@@ -4359,7 +4356,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B25">
         <v>3</v>
@@ -4399,7 +4396,7 @@
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B30">
         <v>2</v>
@@ -4415,7 +4412,7 @@
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B32">
         <v>2</v>
@@ -4431,7 +4428,7 @@
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B34">
         <v>1</v>
@@ -4447,7 +4444,7 @@
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B36">
         <v>1</v>
@@ -4455,7 +4452,7 @@
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B37">
         <v>1</v>
@@ -4463,7 +4460,7 @@
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B38">
         <v>1</v>
@@ -4479,7 +4476,7 @@
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B40">
         <v>1</v>
@@ -4487,7 +4484,7 @@
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B41">
         <v>1</v>
@@ -4495,7 +4492,7 @@
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B42">
         <v>1</v>
@@ -4503,7 +4500,7 @@
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B43">
         <v>1</v>
@@ -4511,7 +4508,7 @@
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B44">
         <v>1</v>
@@ -4519,7 +4516,7 @@
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B45">
         <v>1</v>
@@ -4543,7 +4540,7 @@
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B48">
         <v>1</v>
@@ -4551,7 +4548,7 @@
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B49">
         <v>1</v>
@@ -4559,7 +4556,7 @@
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B50">
         <v>1</v>
@@ -4629,15 +4626,15 @@
   <sheetData>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B4" s="11">
         <v>1</v>
@@ -4677,7 +4674,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B9" s="11">
         <v>1</v>
@@ -4685,7 +4682,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B10" s="11">
         <v>27</v>
@@ -4693,7 +4690,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B11" s="11">
         <v>1</v>
@@ -4701,7 +4698,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B12" s="11">
         <v>1</v>
@@ -4709,7 +4706,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B13" s="11">
         <v>11</v>
@@ -4741,7 +4738,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B17" s="11">
         <v>3</v>
@@ -4757,7 +4754,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B19" s="11">
         <v>9</v>
@@ -4765,7 +4762,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="10" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B20" s="11">
         <v>1</v>
@@ -4781,7 +4778,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B22" s="11">
         <v>1</v>
@@ -4789,7 +4786,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="10" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B23" s="11">
         <v>4</v>
@@ -4797,7 +4794,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="10" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B24" s="11">
         <v>4</v>
@@ -4813,7 +4810,7 @@
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B26" s="11">
         <v>1</v>
@@ -4853,7 +4850,7 @@
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B31" s="11">
         <v>3</v>
@@ -4861,7 +4858,7 @@
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B32" s="11">
         <v>1</v>
@@ -4869,7 +4866,7 @@
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B33" s="11">
         <v>3</v>
@@ -4877,7 +4874,7 @@
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="10" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B34" s="11">
         <v>1</v>
@@ -4893,7 +4890,7 @@
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" s="10" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B36" s="11">
         <v>1</v>
@@ -4901,7 +4898,7 @@
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B37" s="11">
         <v>3</v>
@@ -4925,7 +4922,7 @@
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" s="10" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B40" s="11">
         <v>5</v>
@@ -4933,7 +4930,7 @@
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" s="10" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B41" s="11">
         <v>2</v>
@@ -4949,7 +4946,7 @@
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" s="10" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B43" s="11">
         <v>1</v>
@@ -4981,7 +4978,7 @@
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" s="10" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B47" s="11">
         <v>1</v>
@@ -4997,7 +4994,7 @@
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" s="10" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B49" s="11">
         <v>1</v>
@@ -5013,7 +5010,7 @@
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" s="10" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B51" s="11">
         <v>2</v>
@@ -5029,7 +5026,7 @@
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" s="10" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B53" s="11"/>
     </row>
@@ -5043,7 +5040,7 @@
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" s="10" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B55" s="11">
         <v>1</v>
@@ -5051,7 +5048,7 @@
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B56" s="11">
         <v>264</v>
@@ -5096,7 +5093,7 @@
   <sheetData>
     <row r="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="2" spans="2:2" x14ac:dyDescent="0.25">
@@ -5672,7 +5669,7 @@
     <row r="97" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B97" s="2" t="str">
         <f>Resultados!L9</f>
-        <v>Kommo-o</v>
+        <v>kommo</v>
       </c>
     </row>
     <row r="98" spans="2:2" x14ac:dyDescent="0.25">
@@ -6512,7 +6509,7 @@
     <row r="237" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B237" s="2" t="str">
         <f>Resultados!O17</f>
-        <v>Kommo-O</v>
+        <v>kommo</v>
       </c>
     </row>
     <row r="238" spans="2:2" x14ac:dyDescent="0.25">
@@ -6650,7 +6647,7 @@
     <row r="260" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B260" s="2" t="str">
         <f>Resultados!O40</f>
-        <v>Kommo-o</v>
+        <v>kommo</v>
       </c>
     </row>
     <row r="261" spans="2:2" x14ac:dyDescent="0.25">

--- a/resultados_torneo.xlsx
+++ b/resultados_torneo.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\power bi\Liga Peruana\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C9E7A65-3DFB-4A67-991E-06F3CDC0C59C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FFD3C13-F751-4348-8B6B-D58AC95A1D8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1266" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1266" uniqueCount="268">
   <si>
     <t>Semana/Fecha</t>
   </si>
@@ -844,9 +844,6 @@
   </si>
   <si>
     <t>Charizard_Mega_X</t>
-  </si>
-  <si>
-    <t>Garchomp_Mega</t>
   </si>
   <si>
     <t>tauros_paldea_aqua_breed</t>
@@ -4444,8 +4441,8 @@
       <c r="K46" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="L46" s="7" t="s">
-        <v>267</v>
+      <c r="L46" s="2" t="s">
+        <v>152</v>
       </c>
       <c r="M46" s="7" t="s">
         <v>39</v>
@@ -4736,7 +4733,7 @@
         <v>26</v>
       </c>
       <c r="O52" s="7" t="s">
-        <v>181</v>
+        <v>22</v>
       </c>
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
@@ -5097,7 +5094,7 @@
         <v>3</v>
       </c>
       <c r="J60" s="7" t="s">
-        <v>181</v>
+        <v>22</v>
       </c>
       <c r="K60" s="7" t="s">
         <v>180</v>
@@ -5190,8 +5187,8 @@
       <c r="I62" s="7">
         <v>3</v>
       </c>
-      <c r="J62" s="7" t="s">
-        <v>182</v>
+      <c r="J62" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="K62" s="7" t="s">
         <v>23</v>
@@ -5237,8 +5234,8 @@
       <c r="I63" s="7">
         <v>3</v>
       </c>
-      <c r="J63" s="7" t="s">
-        <v>182</v>
+      <c r="J63" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="K63" s="7" t="s">
         <v>21</v>
@@ -5284,8 +5281,8 @@
       <c r="I64" s="7">
         <v>3</v>
       </c>
-      <c r="J64" s="7" t="s">
-        <v>182</v>
+      <c r="J64" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="K64" s="7" t="s">
         <v>87</v>
@@ -5378,8 +5375,8 @@
       <c r="I66" s="7">
         <v>3</v>
       </c>
-      <c r="J66" s="7" t="s">
-        <v>182</v>
+      <c r="J66" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="K66" s="7" t="s">
         <v>185</v>
@@ -5613,8 +5610,8 @@
       <c r="I71" s="7">
         <v>3</v>
       </c>
-      <c r="J71" s="7" t="s">
-        <v>218</v>
+      <c r="J71" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="K71" s="7" t="s">
         <v>219</v>
@@ -6272,7 +6269,7 @@
         <v>3</v>
       </c>
       <c r="J85" s="7" t="s">
-        <v>247</v>
+        <v>154</v>
       </c>
       <c r="K85" s="7" t="s">
         <v>69</v>
@@ -6322,7 +6319,7 @@
         <v>59</v>
       </c>
       <c r="K86" s="7" t="s">
-        <v>181</v>
+        <v>22</v>
       </c>
       <c r="L86" s="7" t="s">
         <v>23</v>
@@ -6333,7 +6330,7 @@
       <c r="N86" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="O86" s="7" t="s">
+      <c r="O86" s="2" t="s">
         <v>26</v>
       </c>
     </row>
@@ -6378,7 +6375,7 @@
         <v>43</v>
       </c>
       <c r="N87" s="7" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="O87" s="7" t="s">
         <v>254</v>
@@ -6415,8 +6412,8 @@
       <c r="J88" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="K88" s="7" t="s">
-        <v>182</v>
+      <c r="K88" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="L88" s="7" t="s">
         <v>67</v>
@@ -6471,7 +6468,7 @@
       <c r="M89" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="N89" s="7" t="s">
+      <c r="N89" s="2" t="s">
         <v>26</v>
       </c>
       <c r="O89" s="7" t="s">

--- a/resultados_torneo.xlsx
+++ b/resultados_torneo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\power bi\Liga Peruana\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AA52C45-7A69-4F42-BD1C-853A6B68888F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E811EDF1-57C9-405D-90F8-52D92BE5E58B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7863,8 +7863,8 @@
       <c r="M53" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="N53" s="7" t="s">
-        <v>179</v>
+      <c r="N53" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="O53" s="7" t="s">
         <v>67</v>
@@ -7911,7 +7911,7 @@
         <v>87</v>
       </c>
       <c r="N54" s="7" t="s">
-        <v>182</v>
+        <v>224</v>
       </c>
       <c r="O54" s="2" t="s">
         <v>26</v>
@@ -8381,7 +8381,7 @@
         <v>26</v>
       </c>
       <c r="N64" s="7" t="s">
-        <v>182</v>
+        <v>224</v>
       </c>
       <c r="O64" s="7" t="s">
         <v>23</v>
@@ -8466,7 +8466,7 @@
         <v>42</v>
       </c>
       <c r="K66" s="7" t="s">
-        <v>182</v>
+        <v>224</v>
       </c>
       <c r="L66" s="7" t="s">
         <v>32</v>
@@ -8651,7 +8651,7 @@
         <v>3</v>
       </c>
       <c r="J70" s="7" t="s">
-        <v>182</v>
+        <v>224</v>
       </c>
       <c r="K70" s="7" t="s">
         <v>32</v>

--- a/resultados_torneo.xlsx
+++ b/resultados_torneo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\power bi\Liga Peruana\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77B20213-263B-4DF2-994A-089A92D83046}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2040D75-FBBF-4973-80B1-6E49F2BC429E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3675" uniqueCount="414">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3675" uniqueCount="413">
   <si>
     <t>Semana/Fecha</t>
   </si>
@@ -1079,9 +1079,6 @@
     <t>N...</t>
   </si>
   <si>
-    <t>Arcanine-Hisui</t>
-  </si>
-  <si>
     <t>Marsh</t>
   </si>
   <si>
@@ -1139,9 +1136,6 @@
     <t>Fabricio</t>
   </si>
   <si>
-    <t>Crabominable Mega</t>
-  </si>
-  <si>
     <t>Gallade</t>
   </si>
   <si>
@@ -1284,6 +1278,9 @@
   </si>
   <si>
     <t>week3</t>
+  </si>
+  <si>
+    <t>Arcanine_Hisui</t>
   </si>
 </sst>
 </file>
@@ -12956,7 +12953,7 @@
         <v>155</v>
       </c>
       <c r="O170" t="s">
-        <v>345</v>
+        <v>412</v>
       </c>
     </row>
     <row r="171" spans="1:15" x14ac:dyDescent="0.25">
@@ -13011,10 +13008,10 @@
         <v>338</v>
       </c>
       <c r="B172" t="s">
+        <v>345</v>
+      </c>
+      <c r="C172" t="s">
         <v>346</v>
-      </c>
-      <c r="C172" t="s">
-        <v>347</v>
       </c>
       <c r="D172" t="s">
         <v>80</v>
@@ -13023,7 +13020,7 @@
         <v>146</v>
       </c>
       <c r="F172" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G172" t="s">
         <v>80</v>
@@ -13058,10 +13055,10 @@
         <v>338</v>
       </c>
       <c r="B173" t="s">
+        <v>345</v>
+      </c>
+      <c r="C173" t="s">
         <v>346</v>
-      </c>
-      <c r="C173" t="s">
-        <v>347</v>
       </c>
       <c r="D173" t="s">
         <v>80</v>
@@ -13102,7 +13099,7 @@
     </row>
     <row r="174" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B174" t="s">
         <v>197</v>
@@ -13149,7 +13146,7 @@
     </row>
     <row r="175" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B175" t="s">
         <v>197</v>
@@ -13196,13 +13193,13 @@
     </row>
     <row r="176" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B176" t="s">
         <v>325</v>
       </c>
       <c r="C176" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D176" t="s">
         <v>163</v>
@@ -13243,13 +13240,13 @@
     </row>
     <row r="177" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B177" t="s">
         <v>325</v>
       </c>
       <c r="C177" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D177" t="s">
         <v>163</v>
@@ -13290,7 +13287,7 @@
     </row>
     <row r="178" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B178" t="s">
         <v>281</v>
@@ -13337,7 +13334,7 @@
     </row>
     <row r="179" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B179" t="s">
         <v>281</v>
@@ -13384,7 +13381,7 @@
     </row>
     <row r="180" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B180" t="s">
         <v>319</v>
@@ -13431,7 +13428,7 @@
     </row>
     <row r="181" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B181" t="s">
         <v>319</v>
@@ -13478,13 +13475,13 @@
     </row>
     <row r="182" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B182" t="s">
         <v>111</v>
       </c>
       <c r="C182" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D182" t="s">
         <v>163</v>
@@ -13525,13 +13522,13 @@
     </row>
     <row r="183" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B183" t="s">
         <v>111</v>
       </c>
       <c r="C183" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D183" t="s">
         <v>163</v>
@@ -13572,13 +13569,13 @@
     </row>
     <row r="184" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B184" t="s">
+        <v>350</v>
+      </c>
+      <c r="C184" t="s">
         <v>351</v>
-      </c>
-      <c r="C184" t="s">
-        <v>352</v>
       </c>
       <c r="D184" t="s">
         <v>80</v>
@@ -13619,13 +13616,13 @@
     </row>
     <row r="185" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B185" t="s">
+        <v>350</v>
+      </c>
+      <c r="C185" t="s">
         <v>351</v>
-      </c>
-      <c r="C185" t="s">
-        <v>352</v>
       </c>
       <c r="D185" t="s">
         <v>80</v>
@@ -13634,7 +13631,7 @@
         <v>146</v>
       </c>
       <c r="F185" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="G185" t="s">
         <v>146</v>
@@ -13666,7 +13663,7 @@
     </row>
     <row r="186" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B186" t="s">
         <v>144</v>
@@ -13713,7 +13710,7 @@
     </row>
     <row r="187" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B187" t="s">
         <v>144</v>
@@ -13760,13 +13757,13 @@
     </row>
     <row r="188" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B188" t="s">
         <v>217</v>
       </c>
       <c r="C188" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D188" t="s">
         <v>163</v>
@@ -13807,13 +13804,13 @@
     </row>
     <row r="189" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B189" t="s">
         <v>217</v>
       </c>
       <c r="C189" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D189" t="s">
         <v>163</v>
@@ -13854,13 +13851,13 @@
     </row>
     <row r="190" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B190" t="s">
         <v>234</v>
       </c>
       <c r="C190" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D190" t="s">
         <v>51</v>
@@ -13901,13 +13898,13 @@
     </row>
     <row r="191" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B191" t="s">
         <v>234</v>
       </c>
       <c r="C191" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D191" t="s">
         <v>51</v>
@@ -13916,7 +13913,7 @@
         <v>63</v>
       </c>
       <c r="F191" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G191" t="s">
         <v>63</v>
@@ -13948,13 +13945,13 @@
     </row>
     <row r="192" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B192" t="s">
+        <v>355</v>
+      </c>
+      <c r="C192" t="s">
         <v>356</v>
-      </c>
-      <c r="C192" t="s">
-        <v>357</v>
       </c>
       <c r="D192" t="s">
         <v>133</v>
@@ -13995,13 +13992,13 @@
     </row>
     <row r="193" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B193" t="s">
+        <v>355</v>
+      </c>
+      <c r="C193" t="s">
         <v>356</v>
-      </c>
-      <c r="C193" t="s">
-        <v>357</v>
       </c>
       <c r="D193" t="s">
         <v>133</v>
@@ -14042,13 +14039,13 @@
     </row>
     <row r="194" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B194" t="s">
+        <v>357</v>
+      </c>
+      <c r="C194" t="s">
         <v>358</v>
-      </c>
-      <c r="C194" t="s">
-        <v>359</v>
       </c>
       <c r="D194" t="s">
         <v>63</v>
@@ -14057,7 +14054,7 @@
         <v>51</v>
       </c>
       <c r="F194" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="G194" t="s">
         <v>63</v>
@@ -14089,13 +14086,13 @@
     </row>
     <row r="195" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B195" t="s">
+        <v>357</v>
+      </c>
+      <c r="C195" t="s">
         <v>358</v>
-      </c>
-      <c r="C195" t="s">
-        <v>359</v>
       </c>
       <c r="D195" t="s">
         <v>63</v>
@@ -14136,13 +14133,13 @@
     </row>
     <row r="196" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
+        <v>360</v>
+      </c>
+      <c r="B196" t="s">
         <v>361</v>
       </c>
-      <c r="B196" t="s">
+      <c r="C196" t="s">
         <v>362</v>
-      </c>
-      <c r="C196" t="s">
-        <v>363</v>
       </c>
       <c r="D196" t="s">
         <v>108</v>
@@ -14151,7 +14148,7 @@
         <v>19</v>
       </c>
       <c r="F196" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="G196" t="s">
         <v>108</v>
@@ -14163,13 +14160,13 @@
         <v>5</v>
       </c>
       <c r="J196" t="s">
-        <v>365</v>
+        <v>173</v>
       </c>
       <c r="K196" t="s">
         <v>39</v>
       </c>
       <c r="L196" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="M196" t="s">
         <v>38</v>
@@ -14183,13 +14180,13 @@
     </row>
     <row r="197" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
+        <v>360</v>
+      </c>
+      <c r="B197" t="s">
         <v>361</v>
       </c>
-      <c r="B197" t="s">
+      <c r="C197" t="s">
         <v>362</v>
-      </c>
-      <c r="C197" t="s">
-        <v>363</v>
       </c>
       <c r="D197" t="s">
         <v>108</v>
@@ -14198,7 +14195,7 @@
         <v>19</v>
       </c>
       <c r="F197" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="G197" t="s">
         <v>19</v>
@@ -14230,13 +14227,13 @@
     </row>
     <row r="198" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B198" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C198" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="D198" t="s">
         <v>108</v>
@@ -14245,7 +14242,7 @@
         <v>19</v>
       </c>
       <c r="F198" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="G198" t="s">
         <v>108</v>
@@ -14277,13 +14274,13 @@
     </row>
     <row r="199" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B199" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C199" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="D199" t="s">
         <v>108</v>
@@ -14324,13 +14321,13 @@
     </row>
     <row r="200" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B200" t="s">
         <v>281</v>
       </c>
       <c r="C200" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="D200" t="s">
         <v>19</v>
@@ -14371,13 +14368,13 @@
     </row>
     <row r="201" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B201" t="s">
         <v>281</v>
       </c>
       <c r="C201" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="D201" t="s">
         <v>19</v>
@@ -14418,13 +14415,13 @@
     </row>
     <row r="202" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B202" t="s">
         <v>311</v>
       </c>
       <c r="C202" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="D202" t="s">
         <v>19</v>
@@ -14465,13 +14462,13 @@
     </row>
     <row r="203" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B203" t="s">
         <v>311</v>
       </c>
       <c r="C203" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="D203" t="s">
         <v>19</v>
@@ -14480,7 +14477,7 @@
         <v>108</v>
       </c>
       <c r="F203" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="G203" t="s">
         <v>108</v>
@@ -14512,7 +14509,7 @@
     </row>
     <row r="204" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B204" t="s">
         <v>241</v>
@@ -14559,7 +14556,7 @@
     </row>
     <row r="205" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B205" t="s">
         <v>241</v>
@@ -14606,13 +14603,13 @@
     </row>
     <row r="206" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B206" t="s">
         <v>226</v>
       </c>
       <c r="C206" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="D206" t="s">
         <v>63</v>
@@ -14653,13 +14650,13 @@
     </row>
     <row r="207" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B207" t="s">
         <v>226</v>
       </c>
       <c r="C207" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="D207" t="s">
         <v>63</v>
@@ -14700,13 +14697,13 @@
     </row>
     <row r="208" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B208" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C208" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="D208" t="s">
         <v>108</v>
@@ -14715,7 +14712,7 @@
         <v>19</v>
       </c>
       <c r="F208" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="G208" t="s">
         <v>108</v>
@@ -14747,13 +14744,13 @@
     </row>
     <row r="209" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B209" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C209" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="D209" t="s">
         <v>108</v>
@@ -14789,18 +14786,18 @@
         <v>32</v>
       </c>
       <c r="O209" t="s">
-        <v>345</v>
+        <v>412</v>
       </c>
     </row>
     <row r="210" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B210" t="s">
         <v>255</v>
       </c>
       <c r="C210" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="D210" t="s">
         <v>19</v>
@@ -14841,13 +14838,13 @@
     </row>
     <row r="211" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B211" t="s">
         <v>255</v>
       </c>
       <c r="C211" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="D211" t="s">
         <v>19</v>
@@ -14856,7 +14853,7 @@
         <v>108</v>
       </c>
       <c r="F211" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="G211" t="s">
         <v>108</v>
@@ -14888,11 +14885,11 @@
     </row>
     <row r="212" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="B212"/>
       <c r="C212" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="D212" t="s">
         <v>80</v>
@@ -14933,11 +14930,11 @@
     </row>
     <row r="213" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="B213"/>
       <c r="C213" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="D213" t="s">
         <v>80</v>
@@ -14946,7 +14943,7 @@
         <v>63</v>
       </c>
       <c r="F213" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G213" t="s">
         <v>63</v>
@@ -14978,13 +14975,13 @@
     </row>
     <row r="214" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
+        <v>373</v>
+      </c>
+      <c r="B214" t="s">
+        <v>374</v>
+      </c>
+      <c r="C214" t="s">
         <v>375</v>
-      </c>
-      <c r="B214" t="s">
-        <v>376</v>
-      </c>
-      <c r="C214" t="s">
-        <v>377</v>
       </c>
       <c r="D214" t="s">
         <v>19</v>
@@ -14993,7 +14990,7 @@
         <v>51</v>
       </c>
       <c r="F214" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="G214" t="s">
         <v>19</v>
@@ -15025,13 +15022,13 @@
     </row>
     <row r="215" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
+        <v>373</v>
+      </c>
+      <c r="B215" t="s">
+        <v>374</v>
+      </c>
+      <c r="C215" t="s">
         <v>375</v>
-      </c>
-      <c r="B215" t="s">
-        <v>376</v>
-      </c>
-      <c r="C215" t="s">
-        <v>377</v>
       </c>
       <c r="D215" t="s">
         <v>19</v>
@@ -15072,13 +15069,13 @@
     </row>
     <row r="216" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B216" t="s">
         <v>136</v>
       </c>
       <c r="C216" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="D216" t="s">
         <v>304</v>
@@ -15119,13 +15116,13 @@
     </row>
     <row r="217" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B217" t="s">
         <v>136</v>
       </c>
       <c r="C217" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="D217" t="s">
         <v>304</v>
@@ -15166,13 +15163,13 @@
     </row>
     <row r="218" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B218" t="s">
         <v>255</v>
       </c>
       <c r="C218" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="D218" t="s">
         <v>19</v>
@@ -15213,13 +15210,13 @@
     </row>
     <row r="219" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B219" t="s">
         <v>255</v>
       </c>
       <c r="C219" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="D219" t="s">
         <v>19</v>
@@ -15260,13 +15257,13 @@
     </row>
     <row r="220" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B220" t="s">
         <v>177</v>
       </c>
       <c r="C220" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="D220" t="s">
         <v>304</v>
@@ -15289,13 +15286,13 @@
     </row>
     <row r="221" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B221" t="s">
         <v>177</v>
       </c>
       <c r="C221" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="D221" t="s">
         <v>304</v>
@@ -15318,13 +15315,13 @@
     </row>
     <row r="222" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B222" t="s">
         <v>277</v>
       </c>
       <c r="C222" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="D222" t="s">
         <v>51</v>
@@ -15365,13 +15362,13 @@
     </row>
     <row r="223" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B223" t="s">
         <v>277</v>
       </c>
       <c r="C223" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="D223" t="s">
         <v>51</v>
@@ -15412,13 +15409,13 @@
     </row>
     <row r="224" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B224" t="s">
         <v>289</v>
       </c>
       <c r="C224" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="D224" t="s">
         <v>51</v>
@@ -15459,13 +15456,13 @@
     </row>
     <row r="225" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B225" t="s">
         <v>289</v>
       </c>
       <c r="C225" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="D225" t="s">
         <v>51</v>
@@ -15506,13 +15503,13 @@
     </row>
     <row r="226" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B226" t="s">
         <v>123</v>
       </c>
       <c r="C226" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="D226" t="s">
         <v>304</v>
@@ -15553,13 +15550,13 @@
     </row>
     <row r="227" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B227" t="s">
         <v>123</v>
       </c>
       <c r="C227" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="D227" t="s">
         <v>304</v>
@@ -15600,13 +15597,13 @@
     </row>
     <row r="228" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B228" t="s">
         <v>177</v>
       </c>
       <c r="C228" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="D228" t="s">
         <v>304</v>
@@ -15647,13 +15644,13 @@
     </row>
     <row r="229" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B229" t="s">
         <v>177</v>
       </c>
       <c r="C229" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="D229" t="s">
         <v>304</v>
@@ -15694,13 +15691,13 @@
     </row>
     <row r="230" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B230" t="s">
         <v>16</v>
       </c>
       <c r="C230" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="D230" t="s">
         <v>80</v>
@@ -15723,13 +15720,13 @@
     </row>
     <row r="231" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B231" t="s">
         <v>16</v>
       </c>
       <c r="C231" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="D231" t="s">
         <v>80</v>
@@ -15752,13 +15749,13 @@
     </row>
     <row r="232" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B232" t="s">
         <v>255</v>
       </c>
       <c r="C232" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="D232" t="s">
         <v>80</v>
@@ -15799,13 +15796,13 @@
     </row>
     <row r="233" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B233" t="s">
         <v>255</v>
       </c>
       <c r="C233" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="D233" t="s">
         <v>80</v>
@@ -15846,13 +15843,13 @@
     </row>
     <row r="234" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="B234" t="s">
         <v>144</v>
       </c>
       <c r="C234" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="D234" t="s">
         <v>146</v>
@@ -15893,13 +15890,13 @@
     </row>
     <row r="235" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="B235" t="s">
         <v>144</v>
       </c>
       <c r="C235" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="D235" t="s">
         <v>146</v>
@@ -15940,13 +15937,13 @@
     </row>
     <row r="236" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="B236" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C236" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="D236" t="s">
         <v>80</v>
@@ -15955,7 +15952,7 @@
         <v>63</v>
       </c>
       <c r="F236" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="G236" t="s">
         <v>80</v>
@@ -15987,13 +15984,13 @@
     </row>
     <row r="237" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="B237" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C237" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="D237" t="s">
         <v>80</v>
@@ -16017,7 +16014,7 @@
         <v>69</v>
       </c>
       <c r="K237" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="L237" t="s">
         <v>42</v>
@@ -16034,13 +16031,13 @@
     </row>
     <row r="238" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="B238" t="s">
         <v>291</v>
       </c>
       <c r="C238" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="D238" t="s">
         <v>63</v>
@@ -16081,13 +16078,13 @@
     </row>
     <row r="239" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="B239" t="s">
         <v>291</v>
       </c>
       <c r="C239" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="D239" t="s">
         <v>63</v>
@@ -16096,7 +16093,7 @@
         <v>80</v>
       </c>
       <c r="F239" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="G239" t="s">
         <v>80</v>
@@ -16128,13 +16125,13 @@
     </row>
     <row r="240" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="B240" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="C240" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="D240" t="s">
         <v>63</v>
@@ -16143,7 +16140,7 @@
         <v>80</v>
       </c>
       <c r="F240" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="G240" t="s">
         <v>63</v>
@@ -16158,7 +16155,7 @@
         <v>69</v>
       </c>
       <c r="K240" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="L240" t="s">
         <v>42</v>
@@ -16175,13 +16172,13 @@
     </row>
     <row r="241" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="B241" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="C241" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="D241" t="s">
         <v>63</v>
@@ -16222,13 +16219,13 @@
     </row>
     <row r="242" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="B242" t="s">
         <v>281</v>
       </c>
       <c r="C242" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="D242" t="s">
         <v>19</v>
@@ -16269,13 +16266,13 @@
     </row>
     <row r="243" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="B243" t="s">
         <v>281</v>
       </c>
       <c r="C243" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="D243" t="s">
         <v>19</v>
@@ -16316,13 +16313,13 @@
     </row>
     <row r="244" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="B244" t="s">
         <v>281</v>
       </c>
       <c r="C244" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="D244" t="s">
         <v>19</v>
@@ -16363,13 +16360,13 @@
     </row>
     <row r="245" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="B245" t="s">
         <v>281</v>
       </c>
       <c r="C245" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="D245" t="s">
         <v>19</v>
@@ -16426,16 +16423,16 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -16670,7 +16667,7 @@
         <v>7</v>
       </c>
       <c r="F18" s="10" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="G18">
         <v>4</v>
@@ -16726,7 +16723,7 @@
         <v>6</v>
       </c>
       <c r="F22" s="10" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="G22">
         <v>3</v>
@@ -16734,7 +16731,7 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="B23">
         <v>6</v>
@@ -16782,7 +16779,7 @@
         <v>5</v>
       </c>
       <c r="F26" s="10" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="G26">
         <v>3</v>
@@ -16846,7 +16843,7 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="B31">
         <v>4</v>
@@ -16866,7 +16863,7 @@
         <v>4</v>
       </c>
       <c r="F32" s="10" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="G32">
         <v>2</v>
@@ -16894,7 +16891,7 @@
         <v>3</v>
       </c>
       <c r="F34" s="10" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="G34">
         <v>2</v>
@@ -16916,7 +16913,7 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="B36">
         <v>3</v>
@@ -17014,13 +17011,13 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="B43">
         <v>2</v>
       </c>
       <c r="F43" s="10" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G43">
         <v>1</v>
@@ -17042,7 +17039,7 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B45">
         <v>2</v>
@@ -17090,7 +17087,7 @@
         <v>2</v>
       </c>
       <c r="F48" s="10" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="G48">
         <v>1</v>
@@ -17132,7 +17129,7 @@
         <v>2</v>
       </c>
       <c r="F51" s="10" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="G51">
         <v>1</v>
@@ -17202,7 +17199,7 @@
         <v>1</v>
       </c>
       <c r="F56" s="10" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="G56">
         <v>1</v>
@@ -17252,7 +17249,7 @@
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="B60">
         <v>1</v>
@@ -17300,7 +17297,7 @@
         <v>1</v>
       </c>
       <c r="F63" s="10" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="G63">
         <v>1</v>
@@ -17308,7 +17305,7 @@
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B64">
         <v>1</v>
@@ -17336,7 +17333,7 @@
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="B66">
         <v>1</v>
@@ -17392,7 +17389,7 @@
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="B70">
         <v>1</v>
@@ -17424,7 +17421,7 @@
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B74">
         <v>1</v>
@@ -17488,7 +17485,7 @@
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B82">
         <v>1</v>
@@ -17504,7 +17501,7 @@
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="B84">
         <v>1</v>
@@ -17520,7 +17517,7 @@
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B86">
         <v>1</v>
@@ -17547,10 +17544,10 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="F1" s="9" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G1" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -17563,10 +17560,10 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="B3" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="F3" s="10" t="s">
         <v>206</v>
@@ -17737,7 +17734,7 @@
         <v>5</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -17751,7 +17748,7 @@
         <v>1</v>
       </c>
       <c r="F16" s="10" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="G16">
         <v>2</v>
@@ -17841,10 +17838,10 @@
         <v>1</v>
       </c>
       <c r="K22" s="9" t="s">
+        <v>405</v>
+      </c>
+      <c r="L22" t="s">
         <v>407</v>
-      </c>
-      <c r="L22" t="s">
-        <v>409</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
@@ -17861,7 +17858,7 @@
         <v>8</v>
       </c>
       <c r="K23" s="10" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="L23">
         <v>1</v>
@@ -17875,13 +17872,13 @@
         <v>4</v>
       </c>
       <c r="F24" s="10" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="G24">
         <v>1</v>
       </c>
       <c r="K24" s="10" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="L24">
         <v>3</v>
@@ -17901,7 +17898,7 @@
         <v>1</v>
       </c>
       <c r="K25" s="10" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="L25">
         <v>4</v>
@@ -17971,7 +17968,7 @@
         <v>3</v>
       </c>
       <c r="F30" s="10" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="G30">
         <v>2</v>
@@ -18027,7 +18024,7 @@
         <v>6</v>
       </c>
       <c r="F34" s="10" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="G34">
         <v>1</v>
@@ -18055,7 +18052,7 @@
         <v>3</v>
       </c>
       <c r="F36" s="10" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="G36">
         <v>4</v>
@@ -18077,7 +18074,7 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="10" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B38">
         <v>1</v>
@@ -18091,7 +18088,7 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="10" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="B39">
         <v>5</v>
@@ -18237,7 +18234,7 @@
         <v>3</v>
       </c>
       <c r="F49" s="10" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="G49">
         <v>1</v>
@@ -18273,7 +18270,7 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="10" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="F52" s="10" t="s">
         <v>205</v>
@@ -18312,7 +18309,7 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="10" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="B55">
         <v>264</v>
@@ -18358,7 +18355,7 @@
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="F60" s="10" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="G60">
         <v>1</v>
@@ -18374,7 +18371,7 @@
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="F62" s="10" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="G62">
         <v>3</v>
@@ -18382,7 +18379,7 @@
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="F63" s="10" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="G63">
         <v>6</v>
@@ -18526,7 +18523,7 @@
     </row>
     <row r="81" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F81" s="10" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="G81">
         <v>528</v>
@@ -18572,10 +18569,10 @@
   <sheetData>
     <row r="1" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="D1" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
     </row>
     <row r="2" spans="2:4" x14ac:dyDescent="0.25">
@@ -18638,7 +18635,7 @@
         <v>#REF!</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9" spans="2:4" x14ac:dyDescent="0.25">
@@ -18683,7 +18680,7 @@
         <v>#REF!</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="14" spans="2:4" x14ac:dyDescent="0.25">
@@ -18800,7 +18797,7 @@
         <v>#REF!</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="27" spans="2:4" x14ac:dyDescent="0.25">
@@ -18890,7 +18887,7 @@
         <v>#REF!</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="37" spans="2:4" x14ac:dyDescent="0.25">
@@ -19106,7 +19103,7 @@
         <v>#REF!</v>
       </c>
       <c r="D60" s="7" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="61" spans="2:4" x14ac:dyDescent="0.25">
@@ -19160,7 +19157,7 @@
         <v>#REF!</v>
       </c>
       <c r="D66" s="7" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="67" spans="2:4" x14ac:dyDescent="0.25">
@@ -19268,7 +19265,7 @@
         <v>#REF!</v>
       </c>
       <c r="D78" s="7" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="79" spans="2:4" x14ac:dyDescent="0.25">
@@ -19313,7 +19310,7 @@
         <v>#REF!</v>
       </c>
       <c r="D83" s="7" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="84" spans="2:4" x14ac:dyDescent="0.25">
@@ -19367,7 +19364,7 @@
         <v>#REF!</v>
       </c>
       <c r="D89" s="7" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
     </row>
     <row r="90" spans="2:4" x14ac:dyDescent="0.25">
@@ -19421,7 +19418,7 @@
         <v>#REF!</v>
       </c>
       <c r="D95" s="7" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="96" spans="2:4" x14ac:dyDescent="0.25">
@@ -19610,7 +19607,7 @@
         <v>#REF!</v>
       </c>
       <c r="D116" s="7" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="117" spans="2:4" x14ac:dyDescent="0.25">
@@ -19673,7 +19670,7 @@
         <v>#REF!</v>
       </c>
       <c r="D123" s="7" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="124" spans="2:4" x14ac:dyDescent="0.25">
@@ -19727,7 +19724,7 @@
         <v>#REF!</v>
       </c>
       <c r="D129" s="7" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="130" spans="2:4" x14ac:dyDescent="0.25">
@@ -20132,7 +20129,7 @@
         <v>#REF!</v>
       </c>
       <c r="D174" s="7" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="175" spans="2:4" x14ac:dyDescent="0.25">
@@ -20231,7 +20228,7 @@
         <v>#REF!</v>
       </c>
       <c r="D185" s="7" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="186" spans="2:4" x14ac:dyDescent="0.25">
@@ -20240,7 +20237,7 @@
         <v>#REF!</v>
       </c>
       <c r="D186" s="7" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="187" spans="2:4" x14ac:dyDescent="0.25">
@@ -20285,7 +20282,7 @@
         <v>#REF!</v>
       </c>
       <c r="D191" s="7" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="192" spans="2:4" x14ac:dyDescent="0.25">
@@ -20303,7 +20300,7 @@
         <v>#REF!</v>
       </c>
       <c r="D193" s="7" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="194" spans="2:4" x14ac:dyDescent="0.25">
@@ -20330,7 +20327,7 @@
         <v>#REF!</v>
       </c>
       <c r="D196" s="7" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="197" spans="2:4" x14ac:dyDescent="0.25">

--- a/resultados_torneo.xlsx
+++ b/resultados_torneo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\power bi\Liga Peruana\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2040D75-FBBF-4973-80B1-6E49F2BC429E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{835722AA-CC30-48EE-A126-03D465E1E43D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1010,9 +1010,6 @@
     <t>Fernando Carlos</t>
   </si>
   <si>
-    <t>Lycanroc-Dusk</t>
-  </si>
-  <si>
     <t>Win STR 2-1 FBZ</t>
   </si>
   <si>
@@ -1281,6 +1278,9 @@
   </si>
   <si>
     <t>Arcanine_Hisui</t>
+  </si>
+  <si>
+    <t>Lycanroc_Dusk</t>
   </si>
 </sst>
 </file>
@@ -11863,7 +11863,7 @@
         <v>24</v>
       </c>
       <c r="L147" t="s">
-        <v>322</v>
+        <v>412</v>
       </c>
       <c r="M147" t="s">
         <v>26</v>
@@ -11883,7 +11883,7 @@
         <v>123</v>
       </c>
       <c r="C148" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D148" t="s">
         <v>304</v>
@@ -11930,7 +11930,7 @@
         <v>123</v>
       </c>
       <c r="C149" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D149" t="s">
         <v>304</v>
@@ -11939,7 +11939,7 @@
         <v>51</v>
       </c>
       <c r="F149" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="G149" t="s">
         <v>51</v>
@@ -11974,10 +11974,10 @@
         <v>315</v>
       </c>
       <c r="B150" t="s">
+        <v>324</v>
+      </c>
+      <c r="C150" t="s">
         <v>325</v>
-      </c>
-      <c r="C150" t="s">
-        <v>326</v>
       </c>
       <c r="D150" t="s">
         <v>163</v>
@@ -11986,7 +11986,7 @@
         <v>146</v>
       </c>
       <c r="F150" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="G150" t="s">
         <v>163</v>
@@ -12007,7 +12007,7 @@
         <v>87</v>
       </c>
       <c r="M150" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="N150" t="s">
         <v>240</v>
@@ -12021,10 +12021,10 @@
         <v>315</v>
       </c>
       <c r="B151" t="s">
+        <v>324</v>
+      </c>
+      <c r="C151" t="s">
         <v>325</v>
-      </c>
-      <c r="C151" t="s">
-        <v>326</v>
       </c>
       <c r="D151" t="s">
         <v>163</v>
@@ -12071,7 +12071,7 @@
         <v>234</v>
       </c>
       <c r="C152" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D152" t="s">
         <v>51</v>
@@ -12080,7 +12080,7 @@
         <v>304</v>
       </c>
       <c r="F152" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G152" t="s">
         <v>304</v>
@@ -12118,7 +12118,7 @@
         <v>234</v>
       </c>
       <c r="C153" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D153" t="s">
         <v>51</v>
@@ -12165,7 +12165,7 @@
         <v>177</v>
       </c>
       <c r="C154" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D154" t="s">
         <v>304</v>
@@ -12212,7 +12212,7 @@
         <v>177</v>
       </c>
       <c r="C155" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D155" t="s">
         <v>304</v>
@@ -12353,7 +12353,7 @@
         <v>136</v>
       </c>
       <c r="C158" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D158" t="s">
         <v>304</v>
@@ -12400,7 +12400,7 @@
         <v>136</v>
       </c>
       <c r="C159" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D159" t="s">
         <v>304</v>
@@ -12409,7 +12409,7 @@
         <v>51</v>
       </c>
       <c r="F159" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="G159" t="s">
         <v>51</v>
@@ -12441,13 +12441,13 @@
     </row>
     <row r="160" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B160" t="s">
         <v>281</v>
       </c>
       <c r="C160" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D160" t="s">
         <v>51</v>
@@ -12456,7 +12456,7 @@
         <v>304</v>
       </c>
       <c r="F160" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="G160" t="s">
         <v>51</v>
@@ -12488,13 +12488,13 @@
     </row>
     <row r="161" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B161" t="s">
         <v>281</v>
       </c>
       <c r="C161" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D161" t="s">
         <v>51</v>
@@ -12503,7 +12503,7 @@
         <v>304</v>
       </c>
       <c r="F161" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="G161" t="s">
         <v>304</v>
@@ -12535,13 +12535,13 @@
     </row>
     <row r="162" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B162" t="s">
+        <v>335</v>
+      </c>
+      <c r="C162" t="s">
         <v>336</v>
-      </c>
-      <c r="C162" t="s">
-        <v>337</v>
       </c>
       <c r="D162" t="s">
         <v>63</v>
@@ -12582,13 +12582,13 @@
     </row>
     <row r="163" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B163" t="s">
+        <v>335</v>
+      </c>
+      <c r="C163" t="s">
         <v>336</v>
-      </c>
-      <c r="C163" t="s">
-        <v>337</v>
       </c>
       <c r="D163" t="s">
         <v>63</v>
@@ -12629,13 +12629,13 @@
     </row>
     <row r="164" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B164" t="s">
         <v>234</v>
       </c>
       <c r="C164" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D164" t="s">
         <v>51</v>
@@ -12676,13 +12676,13 @@
     </row>
     <row r="165" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B165" t="s">
         <v>234</v>
       </c>
       <c r="C165" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D165" t="s">
         <v>51</v>
@@ -12723,13 +12723,13 @@
     </row>
     <row r="166" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B166" t="s">
         <v>246</v>
       </c>
       <c r="C166" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D166" t="s">
         <v>146</v>
@@ -12770,13 +12770,13 @@
     </row>
     <row r="167" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B167" t="s">
         <v>246</v>
       </c>
       <c r="C167" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D167" t="s">
         <v>146</v>
@@ -12785,7 +12785,7 @@
         <v>80</v>
       </c>
       <c r="F167" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="G167" t="s">
         <v>80</v>
@@ -12817,13 +12817,13 @@
     </row>
     <row r="168" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B168" t="s">
+        <v>341</v>
+      </c>
+      <c r="C168" t="s">
         <v>342</v>
-      </c>
-      <c r="C168" t="s">
-        <v>343</v>
       </c>
       <c r="D168" t="s">
         <v>163</v>
@@ -12864,13 +12864,13 @@
     </row>
     <row r="169" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B169" t="s">
+        <v>341</v>
+      </c>
+      <c r="C169" t="s">
         <v>342</v>
-      </c>
-      <c r="C169" t="s">
-        <v>343</v>
       </c>
       <c r="D169" t="s">
         <v>163</v>
@@ -12911,13 +12911,13 @@
     </row>
     <row r="170" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B170" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C170" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D170" t="s">
         <v>163</v>
@@ -12953,18 +12953,18 @@
         <v>155</v>
       </c>
       <c r="O170" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="171" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B171" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C171" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D171" t="s">
         <v>163</v>
@@ -13005,13 +13005,13 @@
     </row>
     <row r="172" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B172" t="s">
+        <v>344</v>
+      </c>
+      <c r="C172" t="s">
         <v>345</v>
-      </c>
-      <c r="C172" t="s">
-        <v>346</v>
       </c>
       <c r="D172" t="s">
         <v>80</v>
@@ -13020,7 +13020,7 @@
         <v>146</v>
       </c>
       <c r="F172" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="G172" t="s">
         <v>80</v>
@@ -13052,13 +13052,13 @@
     </row>
     <row r="173" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B173" t="s">
+        <v>344</v>
+      </c>
+      <c r="C173" t="s">
         <v>345</v>
-      </c>
-      <c r="C173" t="s">
-        <v>346</v>
       </c>
       <c r="D173" t="s">
         <v>80</v>
@@ -13099,13 +13099,13 @@
     </row>
     <row r="174" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B174" t="s">
         <v>197</v>
       </c>
       <c r="C174" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D174" t="s">
         <v>146</v>
@@ -13146,13 +13146,13 @@
     </row>
     <row r="175" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B175" t="s">
         <v>197</v>
       </c>
       <c r="C175" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D175" t="s">
         <v>146</v>
@@ -13193,13 +13193,13 @@
     </row>
     <row r="176" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
+        <v>347</v>
+      </c>
+      <c r="B176" t="s">
+        <v>324</v>
+      </c>
+      <c r="C176" t="s">
         <v>348</v>
-      </c>
-      <c r="B176" t="s">
-        <v>325</v>
-      </c>
-      <c r="C176" t="s">
-        <v>349</v>
       </c>
       <c r="D176" t="s">
         <v>163</v>
@@ -13208,7 +13208,7 @@
         <v>107</v>
       </c>
       <c r="F176" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="G176" t="s">
         <v>163</v>
@@ -13229,7 +13229,7 @@
         <v>179</v>
       </c>
       <c r="M176" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="N176" t="s">
         <v>31</v>
@@ -13240,13 +13240,13 @@
     </row>
     <row r="177" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
+        <v>347</v>
+      </c>
+      <c r="B177" t="s">
+        <v>324</v>
+      </c>
+      <c r="C177" t="s">
         <v>348</v>
-      </c>
-      <c r="B177" t="s">
-        <v>325</v>
-      </c>
-      <c r="C177" t="s">
-        <v>349</v>
       </c>
       <c r="D177" t="s">
         <v>163</v>
@@ -13287,13 +13287,13 @@
     </row>
     <row r="178" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B178" t="s">
         <v>281</v>
       </c>
       <c r="C178" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D178" t="s">
         <v>51</v>
@@ -13302,7 +13302,7 @@
         <v>63</v>
       </c>
       <c r="F178" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="G178" t="s">
         <v>51</v>
@@ -13334,13 +13334,13 @@
     </row>
     <row r="179" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B179" t="s">
         <v>281</v>
       </c>
       <c r="C179" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D179" t="s">
         <v>51</v>
@@ -13381,13 +13381,13 @@
     </row>
     <row r="180" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B180" t="s">
         <v>319</v>
       </c>
       <c r="C180" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D180" t="s">
         <v>163</v>
@@ -13428,13 +13428,13 @@
     </row>
     <row r="181" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B181" t="s">
         <v>319</v>
       </c>
       <c r="C181" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D181" t="s">
         <v>163</v>
@@ -13443,7 +13443,7 @@
         <v>107</v>
       </c>
       <c r="F181" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="G181" t="s">
         <v>107</v>
@@ -13475,13 +13475,13 @@
     </row>
     <row r="182" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B182" t="s">
         <v>111</v>
       </c>
       <c r="C182" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="D182" t="s">
         <v>163</v>
@@ -13522,13 +13522,13 @@
     </row>
     <row r="183" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B183" t="s">
         <v>111</v>
       </c>
       <c r="C183" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="D183" t="s">
         <v>163</v>
@@ -13569,13 +13569,13 @@
     </row>
     <row r="184" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B184" t="s">
+        <v>349</v>
+      </c>
+      <c r="C184" t="s">
         <v>350</v>
-      </c>
-      <c r="C184" t="s">
-        <v>351</v>
       </c>
       <c r="D184" t="s">
         <v>80</v>
@@ -13616,13 +13616,13 @@
     </row>
     <row r="185" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B185" t="s">
+        <v>349</v>
+      </c>
+      <c r="C185" t="s">
         <v>350</v>
-      </c>
-      <c r="C185" t="s">
-        <v>351</v>
       </c>
       <c r="D185" t="s">
         <v>80</v>
@@ -13631,7 +13631,7 @@
         <v>146</v>
       </c>
       <c r="F185" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="G185" t="s">
         <v>146</v>
@@ -13663,13 +13663,13 @@
     </row>
     <row r="186" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B186" t="s">
         <v>144</v>
       </c>
       <c r="C186" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D186" t="s">
         <v>146</v>
@@ -13710,13 +13710,13 @@
     </row>
     <row r="187" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B187" t="s">
         <v>144</v>
       </c>
       <c r="C187" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D187" t="s">
         <v>146</v>
@@ -13757,13 +13757,13 @@
     </row>
     <row r="188" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B188" t="s">
         <v>217</v>
       </c>
       <c r="C188" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="D188" t="s">
         <v>163</v>
@@ -13804,13 +13804,13 @@
     </row>
     <row r="189" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B189" t="s">
         <v>217</v>
       </c>
       <c r="C189" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="D189" t="s">
         <v>163</v>
@@ -13851,13 +13851,13 @@
     </row>
     <row r="190" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B190" t="s">
         <v>234</v>
       </c>
       <c r="C190" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D190" t="s">
         <v>51</v>
@@ -13866,7 +13866,7 @@
         <v>63</v>
       </c>
       <c r="F190" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G190" t="s">
         <v>51</v>
@@ -13898,13 +13898,13 @@
     </row>
     <row r="191" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B191" t="s">
         <v>234</v>
       </c>
       <c r="C191" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D191" t="s">
         <v>51</v>
@@ -13913,7 +13913,7 @@
         <v>63</v>
       </c>
       <c r="F191" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="G191" t="s">
         <v>63</v>
@@ -13945,13 +13945,13 @@
     </row>
     <row r="192" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B192" t="s">
+        <v>354</v>
+      </c>
+      <c r="C192" t="s">
         <v>355</v>
-      </c>
-      <c r="C192" t="s">
-        <v>356</v>
       </c>
       <c r="D192" t="s">
         <v>133</v>
@@ -13992,13 +13992,13 @@
     </row>
     <row r="193" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B193" t="s">
+        <v>354</v>
+      </c>
+      <c r="C193" t="s">
         <v>355</v>
-      </c>
-      <c r="C193" t="s">
-        <v>356</v>
       </c>
       <c r="D193" t="s">
         <v>133</v>
@@ -14039,13 +14039,13 @@
     </row>
     <row r="194" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B194" t="s">
+        <v>356</v>
+      </c>
+      <c r="C194" t="s">
         <v>357</v>
-      </c>
-      <c r="C194" t="s">
-        <v>358</v>
       </c>
       <c r="D194" t="s">
         <v>63</v>
@@ -14054,7 +14054,7 @@
         <v>51</v>
       </c>
       <c r="F194" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="G194" t="s">
         <v>63</v>
@@ -14086,13 +14086,13 @@
     </row>
     <row r="195" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B195" t="s">
+        <v>356</v>
+      </c>
+      <c r="C195" t="s">
         <v>357</v>
-      </c>
-      <c r="C195" t="s">
-        <v>358</v>
       </c>
       <c r="D195" t="s">
         <v>63</v>
@@ -14133,13 +14133,13 @@
     </row>
     <row r="196" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
+        <v>359</v>
+      </c>
+      <c r="B196" t="s">
         <v>360</v>
       </c>
-      <c r="B196" t="s">
+      <c r="C196" t="s">
         <v>361</v>
-      </c>
-      <c r="C196" t="s">
-        <v>362</v>
       </c>
       <c r="D196" t="s">
         <v>108</v>
@@ -14148,7 +14148,7 @@
         <v>19</v>
       </c>
       <c r="F196" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="G196" t="s">
         <v>108</v>
@@ -14166,7 +14166,7 @@
         <v>39</v>
       </c>
       <c r="L196" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="M196" t="s">
         <v>38</v>
@@ -14180,13 +14180,13 @@
     </row>
     <row r="197" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
+        <v>359</v>
+      </c>
+      <c r="B197" t="s">
         <v>360</v>
       </c>
-      <c r="B197" t="s">
+      <c r="C197" t="s">
         <v>361</v>
-      </c>
-      <c r="C197" t="s">
-        <v>362</v>
       </c>
       <c r="D197" t="s">
         <v>108</v>
@@ -14195,7 +14195,7 @@
         <v>19</v>
       </c>
       <c r="F197" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="G197" t="s">
         <v>19</v>
@@ -14227,13 +14227,13 @@
     </row>
     <row r="198" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B198" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C198" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D198" t="s">
         <v>108</v>
@@ -14242,7 +14242,7 @@
         <v>19</v>
       </c>
       <c r="F198" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="G198" t="s">
         <v>108</v>
@@ -14274,13 +14274,13 @@
     </row>
     <row r="199" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B199" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C199" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D199" t="s">
         <v>108</v>
@@ -14321,13 +14321,13 @@
     </row>
     <row r="200" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B200" t="s">
         <v>281</v>
       </c>
       <c r="C200" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="D200" t="s">
         <v>19</v>
@@ -14368,13 +14368,13 @@
     </row>
     <row r="201" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B201" t="s">
         <v>281</v>
       </c>
       <c r="C201" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="D201" t="s">
         <v>19</v>
@@ -14415,13 +14415,13 @@
     </row>
     <row r="202" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B202" t="s">
         <v>311</v>
       </c>
       <c r="C202" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="D202" t="s">
         <v>19</v>
@@ -14462,13 +14462,13 @@
     </row>
     <row r="203" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B203" t="s">
         <v>311</v>
       </c>
       <c r="C203" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="D203" t="s">
         <v>19</v>
@@ -14477,7 +14477,7 @@
         <v>108</v>
       </c>
       <c r="F203" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="G203" t="s">
         <v>108</v>
@@ -14509,13 +14509,13 @@
     </row>
     <row r="204" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B204" t="s">
         <v>241</v>
       </c>
       <c r="C204" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D204" t="s">
         <v>51</v>
@@ -14524,7 +14524,7 @@
         <v>63</v>
       </c>
       <c r="F204" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="G204" t="s">
         <v>51</v>
@@ -14556,13 +14556,13 @@
     </row>
     <row r="205" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B205" t="s">
         <v>241</v>
       </c>
       <c r="C205" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D205" t="s">
         <v>51</v>
@@ -14603,13 +14603,13 @@
     </row>
     <row r="206" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B206" t="s">
         <v>226</v>
       </c>
       <c r="C206" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D206" t="s">
         <v>63</v>
@@ -14650,13 +14650,13 @@
     </row>
     <row r="207" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B207" t="s">
         <v>226</v>
       </c>
       <c r="C207" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D207" t="s">
         <v>63</v>
@@ -14697,13 +14697,13 @@
     </row>
     <row r="208" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B208" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C208" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D208" t="s">
         <v>108</v>
@@ -14712,7 +14712,7 @@
         <v>19</v>
       </c>
       <c r="F208" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="G208" t="s">
         <v>108</v>
@@ -14744,13 +14744,13 @@
     </row>
     <row r="209" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B209" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C209" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D209" t="s">
         <v>108</v>
@@ -14786,18 +14786,18 @@
         <v>32</v>
       </c>
       <c r="O209" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="210" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B210" t="s">
         <v>255</v>
       </c>
       <c r="C210" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="D210" t="s">
         <v>19</v>
@@ -14838,13 +14838,13 @@
     </row>
     <row r="211" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B211" t="s">
         <v>255</v>
       </c>
       <c r="C211" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="D211" t="s">
         <v>19</v>
@@ -14853,7 +14853,7 @@
         <v>108</v>
       </c>
       <c r="F211" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="G211" t="s">
         <v>108</v>
@@ -14885,11 +14885,11 @@
     </row>
     <row r="212" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B212"/>
       <c r="C212" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D212" t="s">
         <v>80</v>
@@ -14930,11 +14930,11 @@
     </row>
     <row r="213" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B213"/>
       <c r="C213" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D213" t="s">
         <v>80</v>
@@ -14943,7 +14943,7 @@
         <v>63</v>
       </c>
       <c r="F213" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="G213" t="s">
         <v>63</v>
@@ -14975,13 +14975,13 @@
     </row>
     <row r="214" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
+        <v>372</v>
+      </c>
+      <c r="B214" t="s">
         <v>373</v>
       </c>
-      <c r="B214" t="s">
+      <c r="C214" t="s">
         <v>374</v>
-      </c>
-      <c r="C214" t="s">
-        <v>375</v>
       </c>
       <c r="D214" t="s">
         <v>19</v>
@@ -14990,7 +14990,7 @@
         <v>51</v>
       </c>
       <c r="F214" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="G214" t="s">
         <v>19</v>
@@ -15022,13 +15022,13 @@
     </row>
     <row r="215" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
+        <v>372</v>
+      </c>
+      <c r="B215" t="s">
         <v>373</v>
       </c>
-      <c r="B215" t="s">
+      <c r="C215" t="s">
         <v>374</v>
-      </c>
-      <c r="C215" t="s">
-        <v>375</v>
       </c>
       <c r="D215" t="s">
         <v>19</v>
@@ -15037,7 +15037,7 @@
         <v>51</v>
       </c>
       <c r="F215" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="G215" t="s">
         <v>51</v>
@@ -15069,13 +15069,13 @@
     </row>
     <row r="216" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B216" t="s">
         <v>136</v>
       </c>
       <c r="C216" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="D216" t="s">
         <v>304</v>
@@ -15116,13 +15116,13 @@
     </row>
     <row r="217" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B217" t="s">
         <v>136</v>
       </c>
       <c r="C217" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="D217" t="s">
         <v>304</v>
@@ -15163,13 +15163,13 @@
     </row>
     <row r="218" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B218" t="s">
         <v>255</v>
       </c>
       <c r="C218" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="D218" t="s">
         <v>19</v>
@@ -15210,13 +15210,13 @@
     </row>
     <row r="219" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B219" t="s">
         <v>255</v>
       </c>
       <c r="C219" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="D219" t="s">
         <v>19</v>
@@ -15257,13 +15257,13 @@
     </row>
     <row r="220" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B220" t="s">
         <v>177</v>
       </c>
       <c r="C220" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="D220" t="s">
         <v>304</v>
@@ -15286,13 +15286,13 @@
     </row>
     <row r="221" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B221" t="s">
         <v>177</v>
       </c>
       <c r="C221" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="D221" t="s">
         <v>304</v>
@@ -15315,13 +15315,13 @@
     </row>
     <row r="222" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B222" t="s">
         <v>277</v>
       </c>
       <c r="C222" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="D222" t="s">
         <v>51</v>
@@ -15362,13 +15362,13 @@
     </row>
     <row r="223" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B223" t="s">
         <v>277</v>
       </c>
       <c r="C223" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="D223" t="s">
         <v>51</v>
@@ -15409,13 +15409,13 @@
     </row>
     <row r="224" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B224" t="s">
         <v>289</v>
       </c>
       <c r="C224" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="D224" t="s">
         <v>51</v>
@@ -15456,13 +15456,13 @@
     </row>
     <row r="225" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B225" t="s">
         <v>289</v>
       </c>
       <c r="C225" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="D225" t="s">
         <v>51</v>
@@ -15503,13 +15503,13 @@
     </row>
     <row r="226" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B226" t="s">
         <v>123</v>
       </c>
       <c r="C226" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="D226" t="s">
         <v>304</v>
@@ -15550,13 +15550,13 @@
     </row>
     <row r="227" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B227" t="s">
         <v>123</v>
       </c>
       <c r="C227" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="D227" t="s">
         <v>304</v>
@@ -15597,13 +15597,13 @@
     </row>
     <row r="228" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B228" t="s">
         <v>177</v>
       </c>
       <c r="C228" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="D228" t="s">
         <v>304</v>
@@ -15612,7 +15612,7 @@
         <v>133</v>
       </c>
       <c r="F228" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="G228" t="s">
         <v>304</v>
@@ -15644,13 +15644,13 @@
     </row>
     <row r="229" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B229" t="s">
         <v>177</v>
       </c>
       <c r="C229" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="D229" t="s">
         <v>304</v>
@@ -15691,13 +15691,13 @@
     </row>
     <row r="230" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B230" t="s">
         <v>16</v>
       </c>
       <c r="C230" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="D230" t="s">
         <v>80</v>
@@ -15720,13 +15720,13 @@
     </row>
     <row r="231" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B231" t="s">
         <v>16</v>
       </c>
       <c r="C231" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="D231" t="s">
         <v>80</v>
@@ -15749,13 +15749,13 @@
     </row>
     <row r="232" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B232" t="s">
         <v>255</v>
       </c>
       <c r="C232" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="D232" t="s">
         <v>80</v>
@@ -15796,13 +15796,13 @@
     </row>
     <row r="233" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B233" t="s">
         <v>255</v>
       </c>
       <c r="C233" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="D233" t="s">
         <v>80</v>
@@ -15843,13 +15843,13 @@
     </row>
     <row r="234" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B234" t="s">
         <v>144</v>
       </c>
       <c r="C234" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="D234" t="s">
         <v>146</v>
@@ -15890,13 +15890,13 @@
     </row>
     <row r="235" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B235" t="s">
         <v>144</v>
       </c>
       <c r="C235" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="D235" t="s">
         <v>146</v>
@@ -15937,13 +15937,13 @@
     </row>
     <row r="236" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B236" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C236" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="D236" t="s">
         <v>80</v>
@@ -15952,7 +15952,7 @@
         <v>63</v>
       </c>
       <c r="F236" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="G236" t="s">
         <v>80</v>
@@ -15984,13 +15984,13 @@
     </row>
     <row r="237" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B237" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C237" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="D237" t="s">
         <v>80</v>
@@ -16014,7 +16014,7 @@
         <v>69</v>
       </c>
       <c r="K237" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="L237" t="s">
         <v>42</v>
@@ -16026,18 +16026,18 @@
         <v>155</v>
       </c>
       <c r="O237" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="238" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B238" t="s">
         <v>291</v>
       </c>
       <c r="C238" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="D238" t="s">
         <v>63</v>
@@ -16078,13 +16078,13 @@
     </row>
     <row r="239" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B239" t="s">
         <v>291</v>
       </c>
       <c r="C239" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="D239" t="s">
         <v>63</v>
@@ -16093,7 +16093,7 @@
         <v>80</v>
       </c>
       <c r="F239" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G239" t="s">
         <v>80</v>
@@ -16125,13 +16125,13 @@
     </row>
     <row r="240" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B240" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C240" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="D240" t="s">
         <v>63</v>
@@ -16140,7 +16140,7 @@
         <v>80</v>
       </c>
       <c r="F240" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="G240" t="s">
         <v>63</v>
@@ -16155,7 +16155,7 @@
         <v>69</v>
       </c>
       <c r="K240" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="L240" t="s">
         <v>42</v>
@@ -16167,18 +16167,18 @@
         <v>155</v>
       </c>
       <c r="O240" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="241" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B241" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C241" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="D241" t="s">
         <v>63</v>
@@ -16219,13 +16219,13 @@
     </row>
     <row r="242" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B242" t="s">
         <v>281</v>
       </c>
       <c r="C242" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="D242" t="s">
         <v>19</v>
@@ -16266,13 +16266,13 @@
     </row>
     <row r="243" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B243" t="s">
         <v>281</v>
       </c>
       <c r="C243" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="D243" t="s">
         <v>19</v>
@@ -16281,7 +16281,7 @@
         <v>51</v>
       </c>
       <c r="F243" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G243" t="s">
         <v>51</v>
@@ -16313,13 +16313,13 @@
     </row>
     <row r="244" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B244" t="s">
         <v>281</v>
       </c>
       <c r="C244" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="D244" t="s">
         <v>19</v>
@@ -16360,13 +16360,13 @@
     </row>
     <row r="245" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B245" t="s">
         <v>281</v>
       </c>
       <c r="C245" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="D245" t="s">
         <v>19</v>
@@ -16375,7 +16375,7 @@
         <v>51</v>
       </c>
       <c r="F245" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="G245" t="s">
         <v>51</v>
@@ -16423,16 +16423,16 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1" s="8" t="s">
         <v>391</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>392</v>
-      </c>
       <c r="F1" s="8" t="s">
+        <v>390</v>
+      </c>
+      <c r="G1" s="8" t="s">
         <v>391</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>392</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -16667,7 +16667,7 @@
         <v>7</v>
       </c>
       <c r="F18" s="10" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="G18">
         <v>4</v>
@@ -16723,7 +16723,7 @@
         <v>6</v>
       </c>
       <c r="F22" s="10" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="G22">
         <v>3</v>
@@ -16731,7 +16731,7 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B23">
         <v>6</v>
@@ -16779,7 +16779,7 @@
         <v>5</v>
       </c>
       <c r="F26" s="10" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="G26">
         <v>3</v>
@@ -16843,7 +16843,7 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B31">
         <v>4</v>
@@ -16863,7 +16863,7 @@
         <v>4</v>
       </c>
       <c r="F32" s="10" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="G32">
         <v>2</v>
@@ -16891,7 +16891,7 @@
         <v>3</v>
       </c>
       <c r="F34" s="10" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="G34">
         <v>2</v>
@@ -16913,7 +16913,7 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B36">
         <v>3</v>
@@ -17011,13 +17011,13 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
+        <v>396</v>
+      </c>
+      <c r="B43">
+        <v>2</v>
+      </c>
+      <c r="F43" s="10" t="s">
         <v>397</v>
-      </c>
-      <c r="B43">
-        <v>2</v>
-      </c>
-      <c r="F43" s="10" t="s">
-        <v>398</v>
       </c>
       <c r="G43">
         <v>1</v>
@@ -17039,7 +17039,7 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B45">
         <v>2</v>
@@ -17087,7 +17087,7 @@
         <v>2</v>
       </c>
       <c r="F48" s="10" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="G48">
         <v>1</v>
@@ -17129,7 +17129,7 @@
         <v>2</v>
       </c>
       <c r="F51" s="10" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="G51">
         <v>1</v>
@@ -17199,7 +17199,7 @@
         <v>1</v>
       </c>
       <c r="F56" s="10" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="G56">
         <v>1</v>
@@ -17249,7 +17249,7 @@
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B60">
         <v>1</v>
@@ -17297,7 +17297,7 @@
         <v>1</v>
       </c>
       <c r="F63" s="10" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="G63">
         <v>1</v>
@@ -17305,7 +17305,7 @@
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B64">
         <v>1</v>
@@ -17333,7 +17333,7 @@
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B66">
         <v>1</v>
@@ -17389,7 +17389,7 @@
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B70">
         <v>1</v>
@@ -17421,7 +17421,7 @@
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B74">
         <v>1</v>
@@ -17485,7 +17485,7 @@
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B82">
         <v>1</v>
@@ -17501,7 +17501,7 @@
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B84">
         <v>1</v>
@@ -17517,7 +17517,7 @@
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B86">
         <v>1</v>
@@ -17544,10 +17544,10 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="F1" s="9" t="s">
+        <v>404</v>
+      </c>
+      <c r="G1" t="s">
         <v>405</v>
-      </c>
-      <c r="G1" t="s">
-        <v>406</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -17560,10 +17560,10 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
+        <v>404</v>
+      </c>
+      <c r="B3" t="s">
         <v>405</v>
-      </c>
-      <c r="B3" t="s">
-        <v>406</v>
       </c>
       <c r="F3" s="10" t="s">
         <v>206</v>
@@ -17734,7 +17734,7 @@
         <v>5</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -17748,7 +17748,7 @@
         <v>1</v>
       </c>
       <c r="F16" s="10" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="G16">
         <v>2</v>
@@ -17838,10 +17838,10 @@
         <v>1</v>
       </c>
       <c r="K22" s="9" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="L22" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
@@ -17858,7 +17858,7 @@
         <v>8</v>
       </c>
       <c r="K23" s="10" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="L23">
         <v>1</v>
@@ -17872,13 +17872,13 @@
         <v>4</v>
       </c>
       <c r="F24" s="10" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="G24">
         <v>1</v>
       </c>
       <c r="K24" s="10" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="L24">
         <v>3</v>
@@ -17898,7 +17898,7 @@
         <v>1</v>
       </c>
       <c r="K25" s="10" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="L25">
         <v>4</v>
@@ -17968,7 +17968,7 @@
         <v>3</v>
       </c>
       <c r="F30" s="10" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="G30">
         <v>2</v>
@@ -18024,7 +18024,7 @@
         <v>6</v>
       </c>
       <c r="F34" s="10" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="G34">
         <v>1</v>
@@ -18052,7 +18052,7 @@
         <v>3</v>
       </c>
       <c r="F36" s="10" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="G36">
         <v>4</v>
@@ -18074,7 +18074,7 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="10" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B38">
         <v>1</v>
@@ -18088,7 +18088,7 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="10" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B39">
         <v>5</v>
@@ -18234,7 +18234,7 @@
         <v>3</v>
       </c>
       <c r="F49" s="10" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="G49">
         <v>1</v>
@@ -18270,7 +18270,7 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="10" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="F52" s="10" t="s">
         <v>205</v>
@@ -18309,7 +18309,7 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="10" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B55">
         <v>264</v>
@@ -18355,7 +18355,7 @@
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="F60" s="10" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="G60">
         <v>1</v>
@@ -18371,7 +18371,7 @@
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="F62" s="10" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="G62">
         <v>3</v>
@@ -18379,7 +18379,7 @@
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="F63" s="10" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="G63">
         <v>6</v>
@@ -18523,7 +18523,7 @@
     </row>
     <row r="81" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F81" s="10" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="G81">
         <v>528</v>
@@ -18569,10 +18569,10 @@
   <sheetData>
     <row r="1" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
+        <v>409</v>
+      </c>
+      <c r="D1" t="s">
         <v>410</v>
-      </c>
-      <c r="D1" t="s">
-        <v>411</v>
       </c>
     </row>
     <row r="2" spans="2:4" x14ac:dyDescent="0.25">
@@ -18635,7 +18635,7 @@
         <v>#REF!</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="9" spans="2:4" x14ac:dyDescent="0.25">
@@ -18680,7 +18680,7 @@
         <v>#REF!</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="14" spans="2:4" x14ac:dyDescent="0.25">
@@ -18797,7 +18797,7 @@
         <v>#REF!</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="27" spans="2:4" x14ac:dyDescent="0.25">
@@ -18887,7 +18887,7 @@
         <v>#REF!</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="37" spans="2:4" x14ac:dyDescent="0.25">
@@ -19103,7 +19103,7 @@
         <v>#REF!</v>
       </c>
       <c r="D60" s="7" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="61" spans="2:4" x14ac:dyDescent="0.25">
@@ -19157,7 +19157,7 @@
         <v>#REF!</v>
       </c>
       <c r="D66" s="7" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="67" spans="2:4" x14ac:dyDescent="0.25">
@@ -19265,7 +19265,7 @@
         <v>#REF!</v>
       </c>
       <c r="D78" s="7" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="79" spans="2:4" x14ac:dyDescent="0.25">
@@ -19310,7 +19310,7 @@
         <v>#REF!</v>
       </c>
       <c r="D83" s="7" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="84" spans="2:4" x14ac:dyDescent="0.25">
@@ -19364,7 +19364,7 @@
         <v>#REF!</v>
       </c>
       <c r="D89" s="7" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="90" spans="2:4" x14ac:dyDescent="0.25">
@@ -19418,7 +19418,7 @@
         <v>#REF!</v>
       </c>
       <c r="D95" s="7" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="96" spans="2:4" x14ac:dyDescent="0.25">
@@ -19607,7 +19607,7 @@
         <v>#REF!</v>
       </c>
       <c r="D116" s="7" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="117" spans="2:4" x14ac:dyDescent="0.25">
@@ -19670,7 +19670,7 @@
         <v>#REF!</v>
       </c>
       <c r="D123" s="7" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="124" spans="2:4" x14ac:dyDescent="0.25">
@@ -19724,7 +19724,7 @@
         <v>#REF!</v>
       </c>
       <c r="D129" s="7" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="130" spans="2:4" x14ac:dyDescent="0.25">
@@ -20129,7 +20129,7 @@
         <v>#REF!</v>
       </c>
       <c r="D174" s="7" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="175" spans="2:4" x14ac:dyDescent="0.25">
@@ -20228,7 +20228,7 @@
         <v>#REF!</v>
       </c>
       <c r="D185" s="7" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="186" spans="2:4" x14ac:dyDescent="0.25">
@@ -20237,7 +20237,7 @@
         <v>#REF!</v>
       </c>
       <c r="D186" s="7" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="187" spans="2:4" x14ac:dyDescent="0.25">
@@ -20282,7 +20282,7 @@
         <v>#REF!</v>
       </c>
       <c r="D191" s="7" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="192" spans="2:4" x14ac:dyDescent="0.25">
@@ -20300,7 +20300,7 @@
         <v>#REF!</v>
       </c>
       <c r="D193" s="7" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="194" spans="2:4" x14ac:dyDescent="0.25">
@@ -20327,7 +20327,7 @@
         <v>#REF!</v>
       </c>
       <c r="D196" s="7" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="197" spans="2:4" x14ac:dyDescent="0.25">
